--- a/scripts/seed-data/source/map-worlds-curation.xlsx
+++ b/scripts/seed-data/source/map-worlds-curation.xlsx
@@ -326,12 +326,18 @@
     <t>Eastern Fringe</t>
   </si>
   <si>
+    <t>mittel; Ostrand der Karte — grobe Regions-Markierung</t>
+  </si>
+  <si>
     <t>pariah_nexus</t>
   </si>
   <si>
     <t>Pariah Nexus</t>
   </si>
   <si>
+    <t>niedrig; Nephilim-Sektor, Ultima (Lexicanum) — grobe Verortung</t>
+  </si>
+  <si>
     <t>spire</t>
   </si>
   <si>
@@ -461,6 +467,12 @@
     <t>Alaxxes Nebula</t>
   </si>
   <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>niedrig; Nebel nahe Fenris (Legacy of Russ)</t>
+  </si>
+  <si>
     <t>antikef</t>
   </si>
   <si>
@@ -581,12 +593,18 @@
     <t>Sanctus Reach</t>
   </si>
   <si>
+    <t>niedrig; Sanctus-Subsektor (Lexicanum)</t>
+  </si>
+  <si>
     <t>tarsis_ultra</t>
   </si>
   <si>
     <t>Tarsis Ultra</t>
   </si>
   <si>
+    <t>niedrig; Ultramarines-Schutzwelt (Warriors of Ultramar) — Position unsicher</t>
+  </si>
+  <si>
     <t>ulthwe</t>
   </si>
   <si>
@@ -611,6 +629,9 @@
     <t>Voltemand</t>
   </si>
   <si>
+    <t>niedrig-mittel; Sabbat-Welt (Ghostmaker)</t>
+  </si>
+  <si>
     <t>aerius</t>
   </si>
   <si>
@@ -623,12 +644,18 @@
     <t>Aexe Cardinal</t>
   </si>
   <si>
+    <t>niedrig-mittel; Sabbat-Welt (Straight Silver)</t>
+  </si>
+  <si>
     <t>alaric_prime</t>
   </si>
   <si>
     <t>Alaric Prime</t>
   </si>
   <si>
+    <t>niedrig; Sanctus Reach, Ultima nahe Obscurus-Grenze (Lexicanum)</t>
+  </si>
+  <si>
     <t>anaxian_line</t>
   </si>
   <si>
@@ -641,6 +668,9 @@
     <t>Ancreon Sextus</t>
   </si>
   <si>
+    <t>niedrig-mittel; Sabbat-Welt (His Last Command)</t>
+  </si>
+  <si>
     <t>astagar</t>
   </si>
   <si>
@@ -653,18 +683,30 @@
     <t>Baal Secundus</t>
   </si>
   <si>
+    <t>baal</t>
+  </si>
+  <si>
+    <t>Mond Baals — Blood-Angels-Rekrutierung</t>
+  </si>
+  <si>
     <t>balhaut</t>
   </si>
   <si>
     <t>Balhaut</t>
   </si>
   <si>
+    <t>mittel; Sabbat-Welt — Slaydos Sieg (Balhaut)</t>
+  </si>
+  <si>
     <t>balopolis</t>
   </si>
   <si>
     <t>Balopolis</t>
   </si>
   <si>
+    <t>niedrig; Sabbat-Welt</t>
+  </si>
+  <si>
     <t>boros_gate</t>
   </si>
   <si>
@@ -689,6 +731,9 @@
     <t>Cirenholm</t>
   </si>
   <si>
+    <t>Stadt auf Phantine (The Guns of Tanith)</t>
+  </si>
+  <si>
     <t>civitas_beati</t>
   </si>
   <si>
@@ -725,6 +770,9 @@
     <t>Dasht i-Kevar</t>
   </si>
   <si>
+    <t>niedrig; T'au-Konfliktraum</t>
+  </si>
+  <si>
     <t>demetrius</t>
   </si>
   <si>
@@ -737,6 +785,12 @@
     <t>Desh'ea</t>
   </si>
   <si>
+    <t>nuceria</t>
+  </si>
+  <si>
+    <t>Stadt auf Nuceria (After Desh'ea)</t>
+  </si>
+  <si>
     <t>diamat</t>
   </si>
   <si>
@@ -749,6 +803,9 @@
     <t>Drakaasi</t>
   </si>
   <si>
+    <t>Daemon-Welt im Eye (Hammer of Daemons)</t>
+  </si>
+  <si>
     <t>dwell</t>
   </si>
   <si>
@@ -767,18 +824,30 @@
     <t>Eternity Gate</t>
   </si>
   <si>
+    <t>Tor des Imperialen Palasts (Siege of Terra)</t>
+  </si>
+  <si>
     <t>ferrozoica</t>
   </si>
   <si>
     <t>Ferrozoica</t>
   </si>
   <si>
+    <t>verghast</t>
+  </si>
+  <si>
+    <t>Zoica-Hive auf Verghast (Necropolis)</t>
+  </si>
+  <si>
     <t>fortis_binary</t>
   </si>
   <si>
     <t>Fortis Binary</t>
   </si>
   <si>
+    <t>niedrig-mittel; Forge World im Sabbat-Cluster (Ghostmaker)</t>
+  </si>
+  <si>
     <t>galaspar</t>
   </si>
   <si>
@@ -797,6 +866,9 @@
     <t>Garm</t>
   </si>
   <si>
+    <t>niedrig-mittel; Space-Wolves-Schreinwelt nahe Fenris (Grey Hunter)</t>
+  </si>
+  <si>
     <t>gondwa_vi</t>
   </si>
   <si>
@@ -809,12 +881,18 @@
     <t>Hagia</t>
   </si>
   <si>
+    <t>mittel; Heilige Welt der Sabbat (Honour Guard)</t>
+  </si>
+  <si>
     <t>herodor</t>
   </si>
   <si>
     <t>Herodor</t>
   </si>
   <si>
+    <t>mittel; Sabbat-Welt (Sabbat Martyr)</t>
+  </si>
+  <si>
     <t>hieronymous_theta</t>
   </si>
   <si>
@@ -827,6 +905,12 @@
     <t>Hinzerhaus</t>
   </si>
   <si>
+    <t>jago</t>
+  </si>
+  <si>
+    <t>Festungshaus auf Jago (Only in Death)</t>
+  </si>
+  <si>
     <t>hive_blackbracken</t>
   </si>
   <si>
@@ -845,6 +929,9 @@
     <t>Hubris</t>
   </si>
   <si>
+    <t>niedrig; Helican-Subsektor (Eisenhorn: Xenos)</t>
+  </si>
+  <si>
     <t>hyades</t>
   </si>
   <si>
@@ -869,12 +956,12 @@
     <t>Iydris</t>
   </si>
   <si>
-    <t>jago</t>
-  </si>
-  <si>
     <t>Jago</t>
   </si>
   <si>
+    <t>niedrig-mittel; Sabbat-Welt (Only in Death)</t>
+  </si>
+  <si>
     <t>jupiter</t>
   </si>
   <si>
@@ -887,6 +974,9 @@
     <t>Kathur</t>
   </si>
   <si>
+    <t>niedrig-mittel; Schreinwelt nahe Cadia (Cadian Blood)</t>
+  </si>
+  <si>
     <t>kiros</t>
   </si>
   <si>
@@ -935,6 +1025,9 @@
     <t>Menazoid Epsilon</t>
   </si>
   <si>
+    <t>mittel; Sabbat-Welt (First and Only)</t>
+  </si>
+  <si>
     <t>monthax</t>
   </si>
   <si>
@@ -971,12 +1064,18 @@
     <t>Perlia</t>
   </si>
   <si>
+    <t>niedrig; Eastern Arm (Cain: Death or Glory)</t>
+  </si>
+  <si>
     <t>pharos</t>
   </si>
   <si>
     <t>Pharos</t>
   </si>
   <si>
+    <t>Der Pharos — Xenos-Leuchtfeuer auf Sotha</t>
+  </si>
+  <si>
     <t>piamen</t>
   </si>
   <si>
@@ -989,6 +1088,12 @@
     <t>Piscina IV</t>
   </si>
   <si>
+    <t>piscina</t>
+  </si>
+  <si>
+    <t>Piscina-System (Purging of Kadillus); IV = Hauptwelt</t>
+  </si>
+  <si>
     <t>port_of_anguish</t>
   </si>
   <si>
@@ -1001,6 +1106,9 @@
     <t>Pyrites</t>
   </si>
   <si>
+    <t>niedrig; Sabbat-Welt (Ghostmaker)</t>
+  </si>
+  <si>
     <t>pythos</t>
   </si>
   <si>
@@ -1013,6 +1121,9 @@
     <t>Queen Mab</t>
   </si>
   <si>
+    <t>Stadt auf Sancour (Bequin)</t>
+  </si>
+  <si>
     <t>rahes_paradise</t>
   </si>
   <si>
@@ -1037,6 +1148,9 @@
     <t>Salvation's Reach</t>
   </si>
   <si>
+    <t>niedrig; Asteroiden-Festung im Sabbat-Raum (Salvation's Reach)</t>
+  </si>
+  <si>
     <t>sedh</t>
   </si>
   <si>
@@ -1061,6 +1175,9 @@
     <t>Sin of Damnation</t>
   </si>
   <si>
+    <t>Space Hulk — keine feste Kartenposition (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>solemnus</t>
   </si>
   <si>
@@ -1073,6 +1190,9 @@
     <t>Spaeton House</t>
   </si>
   <si>
+    <t>Eisenhorns Anwesen auf Gudrun</t>
+  </si>
+  <si>
     <t>stalinvast</t>
   </si>
   <si>
@@ -1085,6 +1205,9 @@
     <t>Steel Tread</t>
   </si>
   <si>
+    <t>Panzer, kein Ort — keine Kartenposition (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>stratos</t>
   </si>
   <si>
@@ -1103,6 +1226,9 @@
     <t>Tartarus</t>
   </si>
   <si>
+    <t>niedrig; Dawn-of-War-Raum nahe Kronus</t>
+  </si>
+  <si>
     <t>terathalion</t>
   </si>
   <si>
@@ -1115,6 +1241,9 @@
     <t>Titan</t>
   </si>
   <si>
+    <t>Sol-System — Festung der Grey Knights</t>
+  </si>
+  <si>
     <t>typhos_prime</t>
   </si>
   <si>
@@ -1139,6 +1268,9 @@
     <t>Vervunhive</t>
   </si>
   <si>
+    <t>Hive auf Verghast (Necropolis)</t>
+  </si>
+  <si>
     <t>visage</t>
   </si>
   <si>
@@ -1151,6 +1283,9 @@
     <t>Yassilli Sarum</t>
   </si>
   <si>
+    <t>niedrig; Scarus (Resolver-Sektor)</t>
+  </si>
+  <si>
     <t>absolom</t>
   </si>
   <si>
@@ -1181,6 +1316,9 @@
     <t>Albia</t>
   </si>
   <si>
+    <t>Region auf Terra (Unification Wars)</t>
+  </si>
+  <si>
     <t>alia</t>
   </si>
   <si>
@@ -1217,6 +1355,12 @@
     <t>Arx Tyrannus</t>
   </si>
   <si>
+    <t>badab</t>
+  </si>
+  <si>
+    <t>Festung der Astral Claws auf Badab Primaris</t>
+  </si>
+  <si>
     <t>attruso</t>
   </si>
   <si>
@@ -1283,12 +1427,18 @@
     <t>Calixis</t>
   </si>
   <si>
+    <t>niedrig-mittel; Calixis-Sektor (Dark Heresy), nahe Halo Stars</t>
+  </si>
+  <si>
     <t>cao_quo</t>
   </si>
   <si>
     <t>Cao Quo</t>
   </si>
   <si>
+    <t>niedrig; T'au-Raum</t>
+  </si>
+  <si>
     <t>castellax</t>
   </si>
   <si>
@@ -1301,6 +1451,9 @@
     <t>Casus Belli</t>
   </si>
   <si>
+    <t>Schiff/Titan — mobil, keine feste Position (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>ceocan</t>
   </si>
   <si>
@@ -1337,6 +1490,12 @@
     <t>Citadel of Vraks</t>
   </si>
   <si>
+    <t>vraks-prime</t>
+  </si>
+  <si>
+    <t>Festung auf Vraks (Siege of Vraks)</t>
+  </si>
+  <si>
     <t>constanix_ii</t>
   </si>
   <si>
@@ -1367,6 +1526,9 @@
     <t>Damask</t>
   </si>
   <si>
+    <t>niedrig; Helican-Subsektor (Eisenhorn)</t>
+  </si>
+  <si>
     <t>darkand</t>
   </si>
   <si>
@@ -1385,6 +1547,9 @@
     <t>Delphic Battlement</t>
   </si>
   <si>
+    <t>Wall-Abschnitt (Siege of Terra)</t>
+  </si>
+  <si>
     <t>diamantus</t>
   </si>
   <si>
@@ -1457,6 +1622,9 @@
     <t>Durer</t>
   </si>
   <si>
+    <t>niedrig; Scarus-Sektor (Eisenhorn)</t>
+  </si>
+  <si>
     <t>ector</t>
   </si>
   <si>
@@ -1469,12 +1637,18 @@
     <t>Eechan</t>
   </si>
   <si>
+    <t>niedrig; Helican-Subsektor (Resolver-Sektor)</t>
+  </si>
+  <si>
     <t>elaras_veil</t>
   </si>
   <si>
     <t>Elara's Veil</t>
   </si>
   <si>
+    <t>niedrig; Spear of the Emperor — jenseits des Rifts</t>
+  </si>
+  <si>
     <t>equixus</t>
   </si>
   <si>
@@ -1487,12 +1661,18 @@
     <t>Kindred of the Eternal Starforge Hold ship</t>
   </si>
   <si>
+    <t>Votann Hold-Schiff — mobil (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>eternity_wall_spaceport</t>
   </si>
   <si>
     <t>Eternity Wall Spaceport</t>
   </si>
   <si>
+    <t>Raumhafen auf Terra (Siege of Terra)</t>
+  </si>
+  <si>
     <t>euphoros</t>
   </si>
   <si>
@@ -1511,6 +1691,9 @@
     <t>Fallen Dome of Periculus</t>
   </si>
   <si>
+    <t>versunkener Dome im Underhive (Periculus)</t>
+  </si>
+  <si>
     <t>fidem_iv</t>
   </si>
   <si>
@@ -1595,12 +1778,18 @@
     <t>Gnostes</t>
   </si>
   <si>
+    <t>niedrig; Sabbat-Region (Resolver-Sektor)</t>
+  </si>
+  <si>
     <t>golden_throne</t>
   </si>
   <si>
     <t>Golden Throne</t>
   </si>
   <si>
+    <t>Thronsaal im Imperialen Palast</t>
+  </si>
+  <si>
     <t>gorro</t>
   </si>
   <si>
@@ -1613,6 +1802,9 @@
     <t>Gravalax</t>
   </si>
   <si>
+    <t>niedrig-mittel; T'au-Grenzraum (For the Emperor)</t>
+  </si>
+  <si>
     <t>grayloc_manor</t>
   </si>
   <si>
@@ -1631,6 +1823,9 @@
     <t>Halo Stars</t>
   </si>
   <si>
+    <t>niedrig; Randregion jenseits Obscurus</t>
+  </si>
+  <si>
     <t>hauts_bassiq</t>
   </si>
   <si>
@@ -1709,30 +1904,45 @@
     <t>Illyrium</t>
   </si>
   <si>
+    <t>Bergregion auf Macragge</t>
+  </si>
+  <si>
     <t>imperial_webway</t>
   </si>
   <si>
     <t>Imperial Webway</t>
   </si>
   <si>
+    <t>Webway-Portal unter dem Palast (The Master of Mankind)</t>
+  </si>
+  <si>
     <t>irkalla</t>
   </si>
   <si>
     <t>Irkalla</t>
   </si>
   <si>
+    <t>Black Ship — mobil (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>iron_blood</t>
   </si>
   <si>
     <t>Iron Blood</t>
   </si>
   <si>
+    <t>Perturabos Flaggschiff — mobil, kein Heimathafen (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>isle_of_st_capilene</t>
   </si>
   <si>
     <t>Isle of St Capilene</t>
   </si>
   <si>
+    <t>auf Sancour (Bequin: Penitent) — mittel</t>
+  </si>
+  <si>
     <t>ithaka</t>
   </si>
   <si>
@@ -1745,18 +1955,30 @@
     <t>Ithraca</t>
   </si>
   <si>
+    <t>calth</t>
+  </si>
+  <si>
+    <t>Stadt auf Calth (Know No Fear)</t>
+  </si>
+  <si>
     <t>junktion</t>
   </si>
   <si>
     <t>Junktion</t>
   </si>
   <si>
+    <t>Underhive-Siedlung (Junktion)</t>
+  </si>
+  <si>
     <t>kadillus_harbour</t>
   </si>
   <si>
     <t>Kadillus Harbour</t>
   </si>
   <si>
+    <t>Stadt auf Piscina IV (Purging of Kadillus)</t>
+  </si>
+  <si>
     <t>kalidar</t>
   </si>
   <si>
@@ -1811,6 +2033,9 @@
     <t>Kronus</t>
   </si>
   <si>
+    <t>niedrig; Dark Crusade (Kronus)</t>
+  </si>
+  <si>
     <t>kurbynola_system</t>
   </si>
   <si>
@@ -1853,6 +2078,9 @@
     <t>Macragge's Honour</t>
   </si>
   <si>
+    <t>Flaggschiff der Ultramarines — Heimathafen (Schiffs-Regel 2026-07-02)</t>
+  </si>
+  <si>
     <t>malodrax</t>
   </si>
   <si>
@@ -1883,6 +2111,12 @@
     <t>Molech's Enlightenment</t>
   </si>
   <si>
+    <t>molech</t>
+  </si>
+  <si>
+    <t>Schiff bei Molech (Vengeful Spirit) — Schiffs-Regel 2026-07-02</t>
+  </si>
+  <si>
     <t>morningstar</t>
   </si>
   <si>
@@ -1913,6 +2147,12 @@
     <t>Northwilds</t>
   </si>
   <si>
+    <t>caliban</t>
+  </si>
+  <si>
+    <t>Region auf Caliban — mittel</t>
+  </si>
+  <si>
     <t>numinus</t>
   </si>
   <si>
@@ -1991,6 +2231,9 @@
     <t>Periremunda</t>
   </si>
   <si>
+    <t>niedrig; Ultima (Cain, Resolver-Sektor)</t>
+  </si>
+  <si>
     <t>phlegethon</t>
   </si>
   <si>
@@ -2033,6 +2276,9 @@
     <t>Quadravidia</t>
   </si>
   <si>
+    <t>niedrig; T'au-Grenzraum (The Greater Good)</t>
+  </si>
+  <si>
     <t>quintus</t>
   </si>
   <si>
@@ -2069,6 +2315,9 @@
     <t>Rezlan VI</t>
   </si>
   <si>
+    <t>niedrig; T'au-Grenzraum (Krieg vs. T'au)</t>
+  </si>
+  <si>
     <t>rilis</t>
   </si>
   <si>
@@ -2111,18 +2360,27 @@
     <t>Saim-Hann</t>
   </si>
   <si>
+    <t>Craftworld — mobil, keine kanonische Position (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>saltire_vex</t>
   </si>
   <si>
     <t>Saltire Vex</t>
   </si>
   <si>
+    <t>niedrig; T'au-Grenzraum</t>
+  </si>
+  <si>
     <t>sanctum_imperialis</t>
   </si>
   <si>
     <t>Sanctum Imperialis</t>
   </si>
   <si>
+    <t>Imperialer Palast</t>
+  </si>
+  <si>
     <t>sandava_ii</t>
   </si>
   <si>
@@ -2183,6 +2441,9 @@
     <t>Sicarus</t>
   </si>
   <si>
+    <t>Daemon-Welt der Word Bearers im Eye</t>
+  </si>
+  <si>
     <t>sigmatus</t>
   </si>
   <si>
@@ -2207,6 +2468,9 @@
     <t>Solace</t>
   </si>
   <si>
+    <t>Schiff — mobil (CC 2026-07-02)</t>
+  </si>
+  <si>
     <t>solo_baston</t>
   </si>
   <si>
@@ -2285,12 +2549,21 @@
     <t>Thramas Sector</t>
   </si>
   <si>
+    <t>mittel; Thramas-Kreuzzug — nahe Tsagualsa</t>
+  </si>
+  <si>
     <t>torvendis</t>
   </si>
   <si>
     <t>Torvendis</t>
   </si>
   <si>
+    <t>the-maelstrom</t>
+  </si>
+  <si>
+    <t>Welt im Maelstrom (Daemon World)</t>
+  </si>
+  <si>
     <t>tsadrekha</t>
   </si>
   <si>
@@ -2303,6 +2576,12 @@
     <t>Urgall Depression</t>
   </si>
   <si>
+    <t>istvaan-v</t>
+  </si>
+  <si>
+    <t>Schlachtfeld des Drop Site Massacre auf Istvaan V</t>
+  </si>
+  <si>
     <t>valoria_quintus</t>
   </si>
   <si>
@@ -2379,6 +2658,9 @@
   </si>
   <si>
     <t>Vraks Prime</t>
+  </si>
+  <si>
+    <t>mittel; Scarus-Sektor (Siege of Vraks)</t>
   </si>
   <si>
     <t>xana_tisiphone</t>
@@ -2538,10 +2820,10 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>3446.61</v>
+        <v>3447</v>
       </c>
       <c r="H2">
-        <v>1604.37</v>
+        <v>1604</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
@@ -2616,10 +2898,10 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>1127.31</v>
+        <v>1127</v>
       </c>
       <c r="H5">
-        <v>4134.53</v>
+        <v>4135</v>
       </c>
       <c r="I5" t="s">
         <v>28</v>
@@ -2711,10 +2993,10 @@
         <v>13</v>
       </c>
       <c r="G9">
-        <v>3488.78</v>
+        <v>3489</v>
       </c>
       <c r="H9">
-        <v>1646.54</v>
+        <v>1647</v>
       </c>
       <c r="I9" t="s">
         <v>14</v>
@@ -2760,10 +3042,10 @@
         <v>13</v>
       </c>
       <c r="G11">
-        <v>5941.63</v>
+        <v>5942</v>
       </c>
       <c r="H11">
-        <v>4380.51</v>
+        <v>4381</v>
       </c>
       <c r="I11" t="s">
         <v>14</v>
@@ -2901,10 +3183,10 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>6468.74</v>
+        <v>6469</v>
       </c>
       <c r="H17">
-        <v>5209.84</v>
+        <v>5210</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>
@@ -2956,10 +3238,10 @@
         <v>13</v>
       </c>
       <c r="G19">
-        <v>5555.08</v>
+        <v>5555</v>
       </c>
       <c r="H19">
-        <v>1674.65</v>
+        <v>1675</v>
       </c>
       <c r="I19" t="s">
         <v>14</v>
@@ -2988,10 +3270,10 @@
         <v>13</v>
       </c>
       <c r="G20">
-        <v>2954.64</v>
+        <v>2955</v>
       </c>
       <c r="H20">
-        <v>5013.05</v>
+        <v>5013</v>
       </c>
       <c r="I20" t="s">
         <v>78</v>
@@ -3089,10 +3371,10 @@
         <v>13</v>
       </c>
       <c r="G24">
-        <v>1654.42</v>
+        <v>1654</v>
       </c>
       <c r="H24">
-        <v>1288.1</v>
+        <v>1288</v>
       </c>
       <c r="I24" t="s">
         <v>93</v>
@@ -3144,10 +3426,10 @@
         <v>13</v>
       </c>
       <c r="G26">
-        <v>4922.54</v>
+        <v>4923</v>
       </c>
       <c r="H26">
-        <v>2222.85</v>
+        <v>2223</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
@@ -3172,16 +3454,31 @@
       <c r="D27">
         <v>2</v>
       </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>6850</v>
+      </c>
+      <c r="H27">
+        <v>3300</v>
+      </c>
+      <c r="I27" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -3189,13 +3486,31 @@
       <c r="D28">
         <v>3</v>
       </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28">
+        <v>4400</v>
+      </c>
+      <c r="H28">
+        <v>2300</v>
+      </c>
+      <c r="I28" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -3210,15 +3525,15 @@
         <v>33</v>
       </c>
       <c r="K29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -3233,15 +3548,15 @@
         <v>89</v>
       </c>
       <c r="K30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -3253,18 +3568,18 @@
         <v>57</v>
       </c>
       <c r="F31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C32">
         <v>4</v>
@@ -3275,10 +3590,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -3290,10 +3605,10 @@
         <v>13</v>
       </c>
       <c r="G33">
-        <v>5871.35</v>
+        <v>5871</v>
       </c>
       <c r="H33">
-        <v>1428.67</v>
+        <v>1429</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -3302,15 +3617,15 @@
         <v>29</v>
       </c>
       <c r="K33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -3322,10 +3637,10 @@
         <v>13</v>
       </c>
       <c r="G34">
-        <v>3024.92</v>
+        <v>3025</v>
       </c>
       <c r="H34">
-        <v>1744.94</v>
+        <v>1745</v>
       </c>
       <c r="I34" t="s">
         <v>93</v>
@@ -3334,15 +3649,15 @@
         <v>29</v>
       </c>
       <c r="K34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -3354,18 +3669,18 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -3377,10 +3692,10 @@
         <v>13</v>
       </c>
       <c r="G36">
-        <v>6307.09</v>
+        <v>6307</v>
       </c>
       <c r="H36">
-        <v>5083.33</v>
+        <v>5083</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
@@ -3389,15 +3704,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -3409,18 +3724,18 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -3431,10 +3746,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -3454,10 +3769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C40">
         <v>4</v>
@@ -3469,10 +3784,10 @@
         <v>13</v>
       </c>
       <c r="G40">
-        <v>1513.86</v>
+        <v>1514</v>
       </c>
       <c r="H40">
-        <v>1372.44</v>
+        <v>1372</v>
       </c>
       <c r="I40" t="s">
         <v>93</v>
@@ -3481,15 +3796,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -3501,10 +3816,10 @@
         <v>13</v>
       </c>
       <c r="G41">
-        <v>6503.88</v>
+        <v>6504</v>
       </c>
       <c r="H41">
-        <v>3818.26</v>
+        <v>3818</v>
       </c>
       <c r="I41" t="s">
         <v>14</v>
@@ -3513,15 +3828,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -3532,10 +3847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -3543,13 +3858,31 @@
       <c r="D43">
         <v>0</v>
       </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43">
+        <v>2950</v>
+      </c>
+      <c r="H43">
+        <v>2250</v>
+      </c>
+      <c r="I43" t="s">
+        <v>150</v>
+      </c>
+      <c r="J43" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -3560,10 +3893,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -3578,15 +3911,15 @@
         <v>51</v>
       </c>
       <c r="K45" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3598,18 +3931,18 @@
         <v>57</v>
       </c>
       <c r="F46" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K46" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -3621,18 +3954,18 @@
         <v>57</v>
       </c>
       <c r="F47" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K47" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -3644,18 +3977,18 @@
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K48" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B49" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -3667,10 +4000,10 @@
         <v>13</v>
       </c>
       <c r="G49">
-        <v>1303.01</v>
+        <v>1303</v>
       </c>
       <c r="H49">
-        <v>4310.23</v>
+        <v>4310</v>
       </c>
       <c r="I49" t="s">
         <v>28</v>
@@ -3679,15 +4012,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -3699,10 +4032,10 @@
         <v>13</v>
       </c>
       <c r="G50">
-        <v>1738.76</v>
+        <v>1739</v>
       </c>
       <c r="H50">
-        <v>1344.33</v>
+        <v>1344</v>
       </c>
       <c r="I50" t="s">
         <v>93</v>
@@ -3711,15 +4044,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -3730,10 +4063,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -3748,15 +4081,15 @@
         <v>24</v>
       </c>
       <c r="K52" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -3768,10 +4101,10 @@
         <v>13</v>
       </c>
       <c r="G53">
-        <v>1794.99</v>
+        <v>1795</v>
       </c>
       <c r="H53">
-        <v>1252.96</v>
+        <v>1253</v>
       </c>
       <c r="I53" t="s">
         <v>93</v>
@@ -3780,15 +4113,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -3800,10 +4133,10 @@
         <v>13</v>
       </c>
       <c r="G54">
-        <v>6257.9</v>
+        <v>6258</v>
       </c>
       <c r="H54">
-        <v>4626.5</v>
+        <v>4627</v>
       </c>
       <c r="I54" t="s">
         <v>14</v>
@@ -3812,15 +4145,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -3832,10 +4165,10 @@
         <v>13</v>
       </c>
       <c r="G55">
-        <v>986.74</v>
+        <v>987</v>
       </c>
       <c r="H55">
-        <v>4345.37</v>
+        <v>4345</v>
       </c>
       <c r="I55" t="s">
         <v>28</v>
@@ -3844,15 +4177,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C56">
         <v>3</v>
@@ -3863,10 +4196,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -3877,10 +4210,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C58">
         <v>3</v>
@@ -3888,13 +4221,31 @@
       <c r="D58">
         <v>0</v>
       </c>
+      <c r="E58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58">
+        <v>3250</v>
+      </c>
+      <c r="H58">
+        <v>1900</v>
+      </c>
+      <c r="I58" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" t="s">
+        <v>29</v>
+      </c>
+      <c r="K58" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -3902,13 +4253,31 @@
       <c r="D59">
         <v>0</v>
       </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59">
+        <v>6050</v>
+      </c>
+      <c r="H59">
+        <v>4980</v>
+      </c>
+      <c r="I59" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -3920,27 +4289,27 @@
         <v>13</v>
       </c>
       <c r="G60">
-        <v>1724.7</v>
+        <v>1725</v>
       </c>
       <c r="H60">
-        <v>1990.92</v>
+        <v>1991</v>
       </c>
       <c r="I60" t="s">
         <v>93</v>
       </c>
       <c r="J60" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="K60" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -3951,10 +4320,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C62">
         <v>3</v>
@@ -3962,13 +4331,31 @@
       <c r="D62">
         <v>0</v>
       </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62">
+        <v>1230</v>
+      </c>
+      <c r="H62">
+        <v>4230</v>
+      </c>
+      <c r="I62" t="s">
+        <v>28</v>
+      </c>
+      <c r="J62" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -3979,10 +4366,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B64" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -3990,13 +4377,31 @@
       <c r="D64">
         <v>0</v>
       </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64">
+        <v>1175</v>
+      </c>
+      <c r="H64">
+        <v>4295</v>
+      </c>
+      <c r="I64" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B65" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -4004,13 +4409,31 @@
       <c r="D65">
         <v>0</v>
       </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65">
+        <v>3270</v>
+      </c>
+      <c r="H65">
+        <v>1930</v>
+      </c>
+      <c r="I65" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B66" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -4021,10 +4444,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B67" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -4032,13 +4455,31 @@
       <c r="D67">
         <v>0</v>
       </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67">
+        <v>1245</v>
+      </c>
+      <c r="H67">
+        <v>4175</v>
+      </c>
+      <c r="I67" t="s">
+        <v>28</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -4049,24 +4490,33 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B69" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69">
         <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" t="s">
+        <v>222</v>
+      </c>
+      <c r="K69" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -4074,13 +4524,31 @@
       <c r="D70">
         <v>0</v>
       </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70">
+        <v>1075</v>
+      </c>
+      <c r="H70">
+        <v>4150</v>
+      </c>
+      <c r="I70" t="s">
+        <v>28</v>
+      </c>
+      <c r="J70" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B71" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -4088,13 +4556,31 @@
       <c r="D71">
         <v>0</v>
       </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71">
+        <v>1155</v>
+      </c>
+      <c r="H71">
+        <v>4385</v>
+      </c>
+      <c r="I71" t="s">
+        <v>28</v>
+      </c>
+      <c r="J71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B72" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -4105,10 +4591,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B73" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -4119,10 +4605,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B74" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C74">
         <v>2</v>
@@ -4133,10 +4619,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -4144,13 +4630,22 @@
       <c r="D75">
         <v>0</v>
       </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>184</v>
+      </c>
+      <c r="K75" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B76" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -4161,10 +4656,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C77">
         <v>2</v>
@@ -4175,10 +4670,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B78" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -4189,10 +4684,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B79" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -4203,10 +4698,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B80" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -4217,10 +4712,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="B81" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -4228,13 +4723,31 @@
       <c r="D81">
         <v>0</v>
       </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81">
+        <v>5900</v>
+      </c>
+      <c r="H81">
+        <v>4550</v>
+      </c>
+      <c r="I81" t="s">
+        <v>14</v>
+      </c>
+      <c r="J81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -4245,10 +4758,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -4256,13 +4769,22 @@
       <c r="D83">
         <v>0</v>
       </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>256</v>
+      </c>
+      <c r="K83" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -4273,10 +4795,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B85" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -4284,13 +4806,22 @@
       <c r="D85">
         <v>0</v>
       </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>85</v>
+      </c>
+      <c r="K85" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="B86" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -4301,10 +4832,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="B87" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -4315,24 +4846,33 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="B88" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88">
         <v>1</v>
+      </c>
+      <c r="E88" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" t="s">
+        <v>24</v>
+      </c>
+      <c r="K88" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B89" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -4340,13 +4880,22 @@
       <c r="D89">
         <v>0</v>
       </c>
+      <c r="E89" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" t="s">
+        <v>272</v>
+      </c>
+      <c r="K89" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="B90" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -4354,13 +4903,31 @@
       <c r="D90">
         <v>0</v>
       </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90">
+        <v>1010</v>
+      </c>
+      <c r="H90">
+        <v>4290</v>
+      </c>
+      <c r="I90" t="s">
+        <v>28</v>
+      </c>
+      <c r="J90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="B91" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -4371,10 +4938,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B92" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -4385,10 +4952,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="B93" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -4396,13 +4963,31 @@
       <c r="D93">
         <v>0</v>
       </c>
+      <c r="E93" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93">
+        <v>2900</v>
+      </c>
+      <c r="H93">
+        <v>2450</v>
+      </c>
+      <c r="I93" t="s">
+        <v>150</v>
+      </c>
+      <c r="J93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="B94" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -4413,10 +4998,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="B95" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -4424,13 +5009,31 @@
       <c r="D95">
         <v>0</v>
       </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95">
+        <v>1090</v>
+      </c>
+      <c r="H95">
+        <v>4230</v>
+      </c>
+      <c r="I95" t="s">
+        <v>28</v>
+      </c>
+      <c r="J95" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="B96" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -4438,13 +5041,31 @@
       <c r="D96">
         <v>0</v>
       </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96">
+        <v>1160</v>
+      </c>
+      <c r="H96">
+        <v>4120</v>
+      </c>
+      <c r="I96" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="B97" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -4455,10 +5076,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="B98" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -4466,13 +5087,22 @@
       <c r="D98">
         <v>0</v>
       </c>
+      <c r="E98" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" t="s">
+        <v>296</v>
+      </c>
+      <c r="K98" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="B99" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -4483,10 +5113,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="B100" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -4497,10 +5127,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="B101" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="C101">
         <v>2</v>
@@ -4508,13 +5138,31 @@
       <c r="D101">
         <v>0</v>
       </c>
+      <c r="E101" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101">
+        <v>1760</v>
+      </c>
+      <c r="H101">
+        <v>1310</v>
+      </c>
+      <c r="I101" t="s">
+        <v>93</v>
+      </c>
+      <c r="J101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K101" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="B102" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -4525,10 +5173,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="B103" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="C103">
         <v>2</v>
@@ -4539,10 +5187,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="B104" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -4553,10 +5201,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="B105" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="C105">
         <v>2</v>
@@ -4567,10 +5215,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B106" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -4578,27 +5226,54 @@
       <c r="D106">
         <v>0</v>
       </c>
+      <c r="E106" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106">
+        <v>1250</v>
+      </c>
+      <c r="H106">
+        <v>4350</v>
+      </c>
+      <c r="I106" t="s">
+        <v>28</v>
+      </c>
+      <c r="J106" t="s">
+        <v>15</v>
+      </c>
+      <c r="K106" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="B107" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="C107">
         <v>1</v>
       </c>
       <c r="D107">
         <v>1</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" t="s">
+        <v>24</v>
+      </c>
+      <c r="K107" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="B108" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -4606,13 +5281,31 @@
       <c r="D108">
         <v>0</v>
       </c>
+      <c r="E108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108">
+        <v>2050</v>
+      </c>
+      <c r="H108">
+        <v>2250</v>
+      </c>
+      <c r="I108" t="s">
+        <v>93</v>
+      </c>
+      <c r="J108" t="s">
+        <v>15</v>
+      </c>
+      <c r="K108" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="B109" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="C109">
         <v>2</v>
@@ -4623,10 +5316,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="B110" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="C110">
         <v>2</v>
@@ -4637,10 +5330,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="B111" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -4651,10 +5344,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="B112" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -4665,10 +5358,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="B113" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -4679,10 +5372,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="B114" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -4693,10 +5386,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="B115" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -4707,10 +5400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="B116" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -4718,13 +5411,31 @@
       <c r="D116">
         <v>0</v>
       </c>
+      <c r="E116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116">
+        <v>1050</v>
+      </c>
+      <c r="H116">
+        <v>4310</v>
+      </c>
+      <c r="I116" t="s">
+        <v>28</v>
+      </c>
+      <c r="J116" t="s">
+        <v>15</v>
+      </c>
+      <c r="K116" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="B117" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -4732,13 +5443,31 @@
       <c r="D117">
         <v>0</v>
       </c>
+      <c r="E117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117">
+        <v>1140</v>
+      </c>
+      <c r="H117">
+        <v>4270</v>
+      </c>
+      <c r="I117" t="s">
+        <v>28</v>
+      </c>
+      <c r="J117" t="s">
+        <v>15</v>
+      </c>
+      <c r="K117" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="B118" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -4749,10 +5478,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="B119" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -4763,10 +5492,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="B120" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -4777,10 +5506,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="B121" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -4788,13 +5517,22 @@
       <c r="D121">
         <v>0</v>
       </c>
+      <c r="E121" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" t="s">
+        <v>184</v>
+      </c>
+      <c r="K121" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="B122" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -4802,13 +5540,31 @@
       <c r="D122">
         <v>0</v>
       </c>
+      <c r="E122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122">
+        <v>5250</v>
+      </c>
+      <c r="H122">
+        <v>3450</v>
+      </c>
+      <c r="I122" t="s">
+        <v>14</v>
+      </c>
+      <c r="J122" t="s">
+        <v>15</v>
+      </c>
+      <c r="K122" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="B123" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -4816,13 +5572,22 @@
       <c r="D123">
         <v>0</v>
       </c>
+      <c r="E123" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" t="s">
+        <v>67</v>
+      </c>
+      <c r="K123" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="B124" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -4833,10 +5598,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="B125" t="s">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -4844,13 +5609,22 @@
       <c r="D125">
         <v>0</v>
       </c>
+      <c r="E125" t="s">
+        <v>57</v>
+      </c>
+      <c r="F125" t="s">
+        <v>357</v>
+      </c>
+      <c r="K125" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="B126" t="s">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -4861,10 +5635,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="B127" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -4872,13 +5646,31 @@
       <c r="D127">
         <v>0</v>
       </c>
+      <c r="E127" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127">
+        <v>1300</v>
+      </c>
+      <c r="H127">
+        <v>4200</v>
+      </c>
+      <c r="I127" t="s">
+        <v>28</v>
+      </c>
+      <c r="J127" t="s">
+        <v>15</v>
+      </c>
+      <c r="K127" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -4889,10 +5681,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="B129" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -4900,13 +5692,22 @@
       <c r="D129">
         <v>0</v>
       </c>
+      <c r="E129" t="s">
+        <v>19</v>
+      </c>
+      <c r="F129" t="s">
+        <v>140</v>
+      </c>
+      <c r="K129" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="B130" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -4917,10 +5718,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="B131" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -4931,10 +5732,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B132" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="C132">
         <v>2</v>
@@ -4945,10 +5746,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="B133" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -4956,13 +5757,31 @@
       <c r="D133">
         <v>0</v>
       </c>
+      <c r="E133" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133">
+        <v>1350</v>
+      </c>
+      <c r="H133">
+        <v>4430</v>
+      </c>
+      <c r="I133" t="s">
+        <v>28</v>
+      </c>
+      <c r="J133" t="s">
+        <v>15</v>
+      </c>
+      <c r="K133" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="B134" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -4973,10 +5792,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="B135" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="C135">
         <v>2</v>
@@ -4987,10 +5806,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="B136" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -5001,10 +5820,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="B137" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="C137">
         <v>2</v>
@@ -5012,13 +5831,16 @@
       <c r="D137">
         <v>0</v>
       </c>
+      <c r="K137" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="B138" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="C138">
         <v>2</v>
@@ -5029,10 +5851,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
       <c r="B139" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="C139">
         <v>2</v>
@@ -5040,13 +5862,22 @@
       <c r="D139">
         <v>0</v>
       </c>
+      <c r="E139" t="s">
+        <v>19</v>
+      </c>
+      <c r="F139" t="s">
+        <v>127</v>
+      </c>
+      <c r="K139" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="B140" t="s">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="C140">
         <v>2</v>
@@ -5057,10 +5888,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="B141" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="C141">
         <v>2</v>
@@ -5068,13 +5899,16 @@
       <c r="D141">
         <v>0</v>
       </c>
+      <c r="K141" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="B142" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="C142">
         <v>2</v>
@@ -5085,10 +5919,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>358</v>
+        <v>399</v>
       </c>
       <c r="B143" t="s">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="C143">
         <v>2</v>
@@ -5099,10 +5933,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>360</v>
+        <v>401</v>
       </c>
       <c r="B144" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="C144">
         <v>2</v>
@@ -5110,13 +5944,31 @@
       <c r="D144">
         <v>0</v>
       </c>
+      <c r="E144" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144">
+        <v>5700</v>
+      </c>
+      <c r="H144">
+        <v>4100</v>
+      </c>
+      <c r="I144" t="s">
+        <v>14</v>
+      </c>
+      <c r="J144" t="s">
+        <v>15</v>
+      </c>
+      <c r="K144" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="B145" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="C145">
         <v>2</v>
@@ -5127,24 +5979,33 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="B146" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146">
         <v>1</v>
+      </c>
+      <c r="E146" t="s">
+        <v>19</v>
+      </c>
+      <c r="F146" t="s">
+        <v>24</v>
+      </c>
+      <c r="K146" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="B147" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="C147">
         <v>2</v>
@@ -5155,10 +6016,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="B148" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
       <c r="C148">
         <v>2</v>
@@ -5169,10 +6030,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="B149" t="s">
-        <v>371</v>
+        <v>414</v>
       </c>
       <c r="C149">
         <v>2</v>
@@ -5183,10 +6044,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>372</v>
+        <v>415</v>
       </c>
       <c r="B150" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -5194,13 +6055,22 @@
       <c r="D150">
         <v>0</v>
       </c>
+      <c r="E150" t="s">
+        <v>19</v>
+      </c>
+      <c r="F150" t="s">
+        <v>272</v>
+      </c>
+      <c r="K150" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>374</v>
+        <v>418</v>
       </c>
       <c r="B151" t="s">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="C151">
         <v>2</v>
@@ -5211,10 +6081,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="B152" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="C152">
         <v>2</v>
@@ -5222,13 +6092,31 @@
       <c r="D152">
         <v>0</v>
       </c>
+      <c r="E152" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152">
+        <v>1620</v>
+      </c>
+      <c r="H152">
+        <v>1330</v>
+      </c>
+      <c r="I152" t="s">
+        <v>93</v>
+      </c>
+      <c r="J152" t="s">
+        <v>15</v>
+      </c>
+      <c r="K152" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="B153" t="s">
-        <v>379</v>
+        <v>424</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5239,10 +6127,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="B154" t="s">
-        <v>381</v>
+        <v>426</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5253,10 +6141,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>382</v>
+        <v>427</v>
       </c>
       <c r="B155" t="s">
-        <v>383</v>
+        <v>428</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5267,10 +6155,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
       <c r="B156" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5281,24 +6169,33 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="B157" t="s">
-        <v>387</v>
+        <v>432</v>
       </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157">
         <v>0</v>
+      </c>
+      <c r="E157" t="s">
+        <v>19</v>
+      </c>
+      <c r="F157" t="s">
+        <v>24</v>
+      </c>
+      <c r="K157" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="B158" t="s">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5309,10 +6206,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>390</v>
+        <v>436</v>
       </c>
       <c r="B159" t="s">
-        <v>391</v>
+        <v>437</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5323,10 +6220,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>392</v>
+        <v>438</v>
       </c>
       <c r="B160" t="s">
-        <v>393</v>
+        <v>439</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5337,10 +6234,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="B161" t="s">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -5351,10 +6248,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="B162" t="s">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -5365,24 +6262,33 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="B163" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163">
         <v>0</v>
+      </c>
+      <c r="E163" t="s">
+        <v>19</v>
+      </c>
+      <c r="F163" t="s">
+        <v>446</v>
+      </c>
+      <c r="K163" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="B164" t="s">
-        <v>401</v>
+        <v>449</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5393,10 +6299,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>402</v>
+        <v>450</v>
       </c>
       <c r="B165" t="s">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5407,10 +6313,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="B166" t="s">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5421,10 +6327,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="B167" t="s">
-        <v>407</v>
+        <v>455</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5435,10 +6341,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>408</v>
+        <v>456</v>
       </c>
       <c r="B168" t="s">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5449,10 +6355,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>410</v>
+        <v>458</v>
       </c>
       <c r="B169" t="s">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5463,10 +6369,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="B170" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5477,10 +6383,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="B171" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -5491,10 +6397,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>416</v>
+        <v>464</v>
       </c>
       <c r="B172" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -5505,10 +6411,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>418</v>
+        <v>466</v>
       </c>
       <c r="B173" t="s">
-        <v>419</v>
+        <v>467</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -5519,38 +6425,74 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="B174" t="s">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174">
         <v>0</v>
+      </c>
+      <c r="E174" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174">
+        <v>1300</v>
+      </c>
+      <c r="H174">
+        <v>1100</v>
+      </c>
+      <c r="I174" t="s">
+        <v>93</v>
+      </c>
+      <c r="J174" t="s">
+        <v>29</v>
+      </c>
+      <c r="K174" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>422</v>
+        <v>471</v>
       </c>
       <c r="B175" t="s">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175">
         <v>0</v>
+      </c>
+      <c r="E175" t="s">
+        <v>13</v>
+      </c>
+      <c r="G175">
+        <v>6200</v>
+      </c>
+      <c r="H175">
+        <v>4550</v>
+      </c>
+      <c r="I175" t="s">
+        <v>14</v>
+      </c>
+      <c r="J175" t="s">
+        <v>15</v>
+      </c>
+      <c r="K175" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="B176" t="s">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -5561,24 +6503,27 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="B177" t="s">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
       <c r="D177">
         <v>0</v>
+      </c>
+      <c r="K177" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>428</v>
+        <v>479</v>
       </c>
       <c r="B178" t="s">
-        <v>429</v>
+        <v>480</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -5589,10 +6534,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>430</v>
+        <v>481</v>
       </c>
       <c r="B179" t="s">
-        <v>431</v>
+        <v>482</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -5603,10 +6548,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>432</v>
+        <v>483</v>
       </c>
       <c r="B180" t="s">
-        <v>433</v>
+        <v>484</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -5617,10 +6562,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>434</v>
+        <v>485</v>
       </c>
       <c r="B181" t="s">
-        <v>435</v>
+        <v>486</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -5631,10 +6576,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>436</v>
+        <v>487</v>
       </c>
       <c r="B182" t="s">
-        <v>437</v>
+        <v>488</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -5645,24 +6590,33 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>438</v>
+        <v>489</v>
       </c>
       <c r="B183" t="s">
-        <v>439</v>
+        <v>490</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183">
         <v>0</v>
+      </c>
+      <c r="E183" t="s">
+        <v>19</v>
+      </c>
+      <c r="F183" t="s">
+        <v>491</v>
+      </c>
+      <c r="K183" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="B184" t="s">
-        <v>441</v>
+        <v>494</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -5673,10 +6627,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="B185" t="s">
-        <v>443</v>
+        <v>496</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -5687,10 +6641,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>444</v>
+        <v>497</v>
       </c>
       <c r="B186" t="s">
-        <v>445</v>
+        <v>498</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -5701,10 +6655,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>446</v>
+        <v>499</v>
       </c>
       <c r="B187" t="s">
-        <v>447</v>
+        <v>500</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -5715,24 +6669,42 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>448</v>
+        <v>501</v>
       </c>
       <c r="B188" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188">
         <v>0</v>
+      </c>
+      <c r="E188" t="s">
+        <v>13</v>
+      </c>
+      <c r="G188">
+        <v>1700</v>
+      </c>
+      <c r="H188">
+        <v>1400</v>
+      </c>
+      <c r="I188" t="s">
+        <v>93</v>
+      </c>
+      <c r="J188" t="s">
+        <v>15</v>
+      </c>
+      <c r="K188" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>450</v>
+        <v>504</v>
       </c>
       <c r="B189" t="s">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -5743,10 +6715,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>452</v>
+        <v>506</v>
       </c>
       <c r="B190" t="s">
-        <v>453</v>
+        <v>507</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -5757,24 +6729,33 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>454</v>
+        <v>508</v>
       </c>
       <c r="B191" t="s">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191">
         <v>0</v>
+      </c>
+      <c r="E191" t="s">
+        <v>19</v>
+      </c>
+      <c r="F191" t="s">
+        <v>24</v>
+      </c>
+      <c r="K191" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>456</v>
+        <v>511</v>
       </c>
       <c r="B192" t="s">
-        <v>457</v>
+        <v>512</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -5785,10 +6766,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="B193" t="s">
-        <v>459</v>
+        <v>514</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -5799,10 +6780,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>460</v>
+        <v>515</v>
       </c>
       <c r="B194" t="s">
-        <v>461</v>
+        <v>516</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -5813,10 +6794,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>462</v>
+        <v>517</v>
       </c>
       <c r="B195" t="s">
-        <v>463</v>
+        <v>518</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -5827,10 +6808,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>464</v>
+        <v>519</v>
       </c>
       <c r="B196" t="s">
-        <v>465</v>
+        <v>520</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -5841,10 +6822,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>466</v>
+        <v>521</v>
       </c>
       <c r="B197" t="s">
-        <v>467</v>
+        <v>522</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -5855,10 +6836,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>468</v>
+        <v>523</v>
       </c>
       <c r="B198" t="s">
-        <v>469</v>
+        <v>524</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -5869,10 +6850,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>470</v>
+        <v>525</v>
       </c>
       <c r="B199" t="s">
-        <v>471</v>
+        <v>526</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -5883,10 +6864,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="B200" t="s">
-        <v>473</v>
+        <v>528</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -5897,10 +6878,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>474</v>
+        <v>529</v>
       </c>
       <c r="B201" t="s">
-        <v>475</v>
+        <v>530</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -5911,10 +6892,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>476</v>
+        <v>531</v>
       </c>
       <c r="B202" t="s">
-        <v>477</v>
+        <v>532</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -5925,24 +6906,42 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>478</v>
+        <v>533</v>
       </c>
       <c r="B203" t="s">
-        <v>479</v>
+        <v>534</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203">
         <v>0</v>
+      </c>
+      <c r="E203" t="s">
+        <v>13</v>
+      </c>
+      <c r="G203">
+        <v>1700</v>
+      </c>
+      <c r="H203">
+        <v>1300</v>
+      </c>
+      <c r="I203" t="s">
+        <v>93</v>
+      </c>
+      <c r="J203" t="s">
+        <v>15</v>
+      </c>
+      <c r="K203" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>480</v>
+        <v>536</v>
       </c>
       <c r="B204" t="s">
-        <v>481</v>
+        <v>537</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -5953,38 +6952,74 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>482</v>
+        <v>538</v>
       </c>
       <c r="B205" t="s">
-        <v>483</v>
+        <v>539</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205">
         <v>0</v>
+      </c>
+      <c r="E205" t="s">
+        <v>13</v>
+      </c>
+      <c r="G205">
+        <v>1780</v>
+      </c>
+      <c r="H205">
+        <v>1370</v>
+      </c>
+      <c r="I205" t="s">
+        <v>93</v>
+      </c>
+      <c r="J205" t="s">
+        <v>15</v>
+      </c>
+      <c r="K205" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>484</v>
+        <v>541</v>
       </c>
       <c r="B206" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206">
         <v>0</v>
+      </c>
+      <c r="E206" t="s">
+        <v>13</v>
+      </c>
+      <c r="G206">
+        <v>6700</v>
+      </c>
+      <c r="H206">
+        <v>4600</v>
+      </c>
+      <c r="I206" t="s">
+        <v>14</v>
+      </c>
+      <c r="J206" t="s">
+        <v>29</v>
+      </c>
+      <c r="K206" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="B207" t="s">
-        <v>487</v>
+        <v>545</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -5995,38 +7030,50 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>488</v>
+        <v>546</v>
       </c>
       <c r="B208" t="s">
-        <v>489</v>
+        <v>547</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208">
         <v>0</v>
+      </c>
+      <c r="K208" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>490</v>
+        <v>549</v>
       </c>
       <c r="B209" t="s">
-        <v>491</v>
+        <v>550</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209">
         <v>0</v>
+      </c>
+      <c r="E209" t="s">
+        <v>19</v>
+      </c>
+      <c r="F209" t="s">
+        <v>24</v>
+      </c>
+      <c r="K209" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>492</v>
+        <v>552</v>
       </c>
       <c r="B210" t="s">
-        <v>493</v>
+        <v>553</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -6037,10 +7084,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>494</v>
+        <v>554</v>
       </c>
       <c r="B211" t="s">
-        <v>495</v>
+        <v>555</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -6051,24 +7098,33 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>496</v>
+        <v>556</v>
       </c>
       <c r="B212" t="s">
-        <v>497</v>
+        <v>557</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212">
         <v>0</v>
+      </c>
+      <c r="E212" t="s">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>33</v>
+      </c>
+      <c r="K212" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>498</v>
+        <v>559</v>
       </c>
       <c r="B213" t="s">
-        <v>499</v>
+        <v>560</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -6079,10 +7135,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>500</v>
+        <v>561</v>
       </c>
       <c r="B214" t="s">
-        <v>501</v>
+        <v>562</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -6093,10 +7149,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>502</v>
+        <v>563</v>
       </c>
       <c r="B215" t="s">
-        <v>503</v>
+        <v>564</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -6107,10 +7163,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>504</v>
+        <v>565</v>
       </c>
       <c r="B216" t="s">
-        <v>505</v>
+        <v>566</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -6121,10 +7177,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>506</v>
+        <v>567</v>
       </c>
       <c r="B217" t="s">
-        <v>507</v>
+        <v>568</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -6135,10 +7191,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>508</v>
+        <v>569</v>
       </c>
       <c r="B218" t="s">
-        <v>509</v>
+        <v>570</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -6149,10 +7205,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>510</v>
+        <v>571</v>
       </c>
       <c r="B219" t="s">
-        <v>511</v>
+        <v>572</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -6163,10 +7219,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>512</v>
+        <v>573</v>
       </c>
       <c r="B220" t="s">
-        <v>513</v>
+        <v>574</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -6177,10 +7233,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>514</v>
+        <v>575</v>
       </c>
       <c r="B221" t="s">
-        <v>515</v>
+        <v>576</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -6191,10 +7247,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>516</v>
+        <v>577</v>
       </c>
       <c r="B222" t="s">
-        <v>517</v>
+        <v>578</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -6205,10 +7261,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>518</v>
+        <v>579</v>
       </c>
       <c r="B223" t="s">
-        <v>519</v>
+        <v>580</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -6219,10 +7275,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="B224" t="s">
-        <v>521</v>
+        <v>582</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -6233,10 +7289,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>522</v>
+        <v>583</v>
       </c>
       <c r="B225" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -6247,38 +7303,65 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>524</v>
+        <v>585</v>
       </c>
       <c r="B226" t="s">
-        <v>525</v>
+        <v>586</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226">
         <v>0</v>
+      </c>
+      <c r="E226" t="s">
+        <v>13</v>
+      </c>
+      <c r="G226">
+        <v>1210</v>
+      </c>
+      <c r="H226">
+        <v>4400</v>
+      </c>
+      <c r="I226" t="s">
+        <v>28</v>
+      </c>
+      <c r="J226" t="s">
+        <v>15</v>
+      </c>
+      <c r="K226" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>526</v>
+        <v>588</v>
       </c>
       <c r="B227" t="s">
-        <v>527</v>
+        <v>589</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227">
         <v>0</v>
+      </c>
+      <c r="E227" t="s">
+        <v>19</v>
+      </c>
+      <c r="F227" t="s">
+        <v>24</v>
+      </c>
+      <c r="K227" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>528</v>
+        <v>591</v>
       </c>
       <c r="B228" t="s">
-        <v>529</v>
+        <v>592</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -6289,24 +7372,42 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>530</v>
+        <v>593</v>
       </c>
       <c r="B229" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229">
         <v>0</v>
+      </c>
+      <c r="E229" t="s">
+        <v>13</v>
+      </c>
+      <c r="G229">
+        <v>5980</v>
+      </c>
+      <c r="H229">
+        <v>4380</v>
+      </c>
+      <c r="I229" t="s">
+        <v>14</v>
+      </c>
+      <c r="J229" t="s">
+        <v>15</v>
+      </c>
+      <c r="K229" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>532</v>
+        <v>596</v>
       </c>
       <c r="B230" t="s">
-        <v>533</v>
+        <v>597</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -6317,38 +7418,65 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>534</v>
+        <v>598</v>
       </c>
       <c r="B231" t="s">
-        <v>535</v>
+        <v>599</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231">
         <v>0</v>
+      </c>
+      <c r="E231" t="s">
+        <v>19</v>
+      </c>
+      <c r="F231" t="s">
+        <v>24</v>
+      </c>
+      <c r="K231" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>536</v>
+        <v>600</v>
       </c>
       <c r="B232" t="s">
-        <v>537</v>
+        <v>601</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232">
         <v>0</v>
+      </c>
+      <c r="E232" t="s">
+        <v>13</v>
+      </c>
+      <c r="G232">
+        <v>1050</v>
+      </c>
+      <c r="H232">
+        <v>700</v>
+      </c>
+      <c r="I232" t="s">
+        <v>93</v>
+      </c>
+      <c r="J232" t="s">
+        <v>29</v>
+      </c>
+      <c r="K232" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>538</v>
+        <v>603</v>
       </c>
       <c r="B233" t="s">
-        <v>539</v>
+        <v>604</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -6359,10 +7487,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>540</v>
+        <v>605</v>
       </c>
       <c r="B234" t="s">
-        <v>541</v>
+        <v>606</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -6373,10 +7501,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="B235" t="s">
-        <v>543</v>
+        <v>608</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -6387,10 +7515,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>544</v>
+        <v>609</v>
       </c>
       <c r="B236" t="s">
-        <v>545</v>
+        <v>610</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -6401,10 +7529,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>546</v>
+        <v>611</v>
       </c>
       <c r="B237" t="s">
-        <v>547</v>
+        <v>612</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -6415,10 +7543,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>548</v>
+        <v>613</v>
       </c>
       <c r="B238" t="s">
-        <v>549</v>
+        <v>614</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -6429,10 +7557,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>550</v>
+        <v>615</v>
       </c>
       <c r="B239" t="s">
-        <v>551</v>
+        <v>616</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -6443,10 +7571,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>552</v>
+        <v>617</v>
       </c>
       <c r="B240" t="s">
-        <v>553</v>
+        <v>618</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -6457,10 +7585,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>554</v>
+        <v>619</v>
       </c>
       <c r="B241" t="s">
-        <v>555</v>
+        <v>620</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -6471,24 +7599,33 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>556</v>
+        <v>621</v>
       </c>
       <c r="B242" t="s">
-        <v>557</v>
+        <v>622</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242">
         <v>0</v>
+      </c>
+      <c r="E242" t="s">
+        <v>19</v>
+      </c>
+      <c r="F242" t="s">
+        <v>24</v>
+      </c>
+      <c r="K242" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>558</v>
+        <v>623</v>
       </c>
       <c r="B243" t="s">
-        <v>559</v>
+        <v>624</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -6499,10 +7636,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>560</v>
+        <v>625</v>
       </c>
       <c r="B244" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -6513,80 +7650,113 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="B245" t="s">
-        <v>563</v>
+        <v>628</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245">
         <v>0</v>
+      </c>
+      <c r="E245" t="s">
+        <v>19</v>
+      </c>
+      <c r="F245" t="s">
+        <v>20</v>
+      </c>
+      <c r="K245" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>564</v>
+        <v>630</v>
       </c>
       <c r="B246" t="s">
-        <v>565</v>
+        <v>631</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246">
         <v>0</v>
+      </c>
+      <c r="E246" t="s">
+        <v>19</v>
+      </c>
+      <c r="F246" t="s">
+        <v>24</v>
+      </c>
+      <c r="K246" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>566</v>
+        <v>633</v>
       </c>
       <c r="B247" t="s">
-        <v>567</v>
+        <v>634</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247">
         <v>0</v>
+      </c>
+      <c r="K247" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>568</v>
+        <v>636</v>
       </c>
       <c r="B248" t="s">
-        <v>569</v>
+        <v>637</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248">
         <v>0</v>
+      </c>
+      <c r="K248" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>570</v>
+        <v>639</v>
       </c>
       <c r="B249" t="s">
-        <v>571</v>
+        <v>640</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249">
         <v>0</v>
+      </c>
+      <c r="E249" t="s">
+        <v>19</v>
+      </c>
+      <c r="F249" t="s">
+        <v>140</v>
+      </c>
+      <c r="K249" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>572</v>
+        <v>642</v>
       </c>
       <c r="B250" t="s">
-        <v>573</v>
+        <v>643</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -6597,52 +7767,79 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>574</v>
+        <v>644</v>
       </c>
       <c r="B251" t="s">
-        <v>575</v>
+        <v>645</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251">
         <v>0</v>
+      </c>
+      <c r="E251" t="s">
+        <v>19</v>
+      </c>
+      <c r="F251" t="s">
+        <v>646</v>
+      </c>
+      <c r="K251" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="B252" t="s">
-        <v>577</v>
+        <v>649</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252">
         <v>0</v>
+      </c>
+      <c r="E252" t="s">
+        <v>19</v>
+      </c>
+      <c r="F252" t="s">
+        <v>33</v>
+      </c>
+      <c r="K252" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>578</v>
+        <v>651</v>
       </c>
       <c r="B253" t="s">
-        <v>579</v>
+        <v>652</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253">
         <v>0</v>
+      </c>
+      <c r="E253" t="s">
+        <v>19</v>
+      </c>
+      <c r="F253" t="s">
+        <v>357</v>
+      </c>
+      <c r="K253" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>580</v>
+        <v>654</v>
       </c>
       <c r="B254" t="s">
-        <v>581</v>
+        <v>655</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -6653,10 +7850,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>582</v>
+        <v>656</v>
       </c>
       <c r="B255" t="s">
-        <v>583</v>
+        <v>657</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -6667,10 +7864,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>584</v>
+        <v>658</v>
       </c>
       <c r="B256" t="s">
-        <v>585</v>
+        <v>659</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -6681,10 +7878,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>586</v>
+        <v>660</v>
       </c>
       <c r="B257" t="s">
-        <v>587</v>
+        <v>661</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -6695,10 +7892,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>588</v>
+        <v>662</v>
       </c>
       <c r="B258" t="s">
-        <v>589</v>
+        <v>663</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -6709,10 +7906,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>590</v>
+        <v>664</v>
       </c>
       <c r="B259" t="s">
-        <v>591</v>
+        <v>665</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -6723,10 +7920,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>592</v>
+        <v>666</v>
       </c>
       <c r="B260" t="s">
-        <v>593</v>
+        <v>667</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -6737,10 +7934,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>594</v>
+        <v>668</v>
       </c>
       <c r="B261" t="s">
-        <v>595</v>
+        <v>669</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -6751,24 +7948,42 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>596</v>
+        <v>670</v>
       </c>
       <c r="B262" t="s">
-        <v>597</v>
+        <v>671</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262">
         <v>0</v>
+      </c>
+      <c r="E262" t="s">
+        <v>13</v>
+      </c>
+      <c r="G262">
+        <v>5900</v>
+      </c>
+      <c r="H262">
+        <v>4250</v>
+      </c>
+      <c r="I262" t="s">
+        <v>14</v>
+      </c>
+      <c r="J262" t="s">
+        <v>15</v>
+      </c>
+      <c r="K262" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>598</v>
+        <v>673</v>
       </c>
       <c r="B263" t="s">
-        <v>599</v>
+        <v>674</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -6779,10 +7994,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="B264" t="s">
-        <v>601</v>
+        <v>676</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -6793,10 +8008,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>602</v>
+        <v>677</v>
       </c>
       <c r="B265" t="s">
-        <v>603</v>
+        <v>678</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -6807,10 +8022,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="B266" t="s">
-        <v>605</v>
+        <v>680</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -6821,10 +8036,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>606</v>
+        <v>681</v>
       </c>
       <c r="B267" t="s">
-        <v>607</v>
+        <v>682</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -6835,10 +8050,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>608</v>
+        <v>683</v>
       </c>
       <c r="B268" t="s">
-        <v>609</v>
+        <v>684</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -6849,24 +8064,33 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>610</v>
+        <v>685</v>
       </c>
       <c r="B269" t="s">
-        <v>611</v>
+        <v>686</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269">
         <v>0</v>
+      </c>
+      <c r="E269" t="s">
+        <v>19</v>
+      </c>
+      <c r="F269" t="s">
+        <v>20</v>
+      </c>
+      <c r="K269" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>612</v>
+        <v>688</v>
       </c>
       <c r="B270" t="s">
-        <v>613</v>
+        <v>689</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -6877,10 +8101,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>614</v>
+        <v>690</v>
       </c>
       <c r="B271" t="s">
-        <v>615</v>
+        <v>691</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -6891,10 +8115,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>616</v>
+        <v>692</v>
       </c>
       <c r="B272" t="s">
-        <v>617</v>
+        <v>693</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -6905,38 +8129,56 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>618</v>
+        <v>694</v>
       </c>
       <c r="B273" t="s">
-        <v>619</v>
+        <v>695</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273">
         <v>0</v>
+      </c>
+      <c r="E273" t="s">
+        <v>19</v>
+      </c>
+      <c r="F273" t="s">
+        <v>24</v>
+      </c>
+      <c r="K273" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>620</v>
+        <v>696</v>
       </c>
       <c r="B274" t="s">
-        <v>621</v>
+        <v>697</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274">
         <v>0</v>
+      </c>
+      <c r="E274" t="s">
+        <v>19</v>
+      </c>
+      <c r="F274" t="s">
+        <v>698</v>
+      </c>
+      <c r="K274" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
       <c r="B275" t="s">
-        <v>623</v>
+        <v>701</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -6947,10 +8189,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>624</v>
+        <v>702</v>
       </c>
       <c r="B276" t="s">
-        <v>625</v>
+        <v>703</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -6961,10 +8203,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>626</v>
+        <v>704</v>
       </c>
       <c r="B277" t="s">
-        <v>627</v>
+        <v>705</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -6975,10 +8217,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>628</v>
+        <v>706</v>
       </c>
       <c r="B278" t="s">
-        <v>629</v>
+        <v>707</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -6989,24 +8231,33 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>630</v>
+        <v>708</v>
       </c>
       <c r="B279" t="s">
-        <v>631</v>
+        <v>709</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279">
         <v>0</v>
+      </c>
+      <c r="E279" t="s">
+        <v>19</v>
+      </c>
+      <c r="F279" t="s">
+        <v>710</v>
+      </c>
+      <c r="K279" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>632</v>
+        <v>712</v>
       </c>
       <c r="B280" t="s">
-        <v>633</v>
+        <v>713</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -7017,10 +8268,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>634</v>
+        <v>714</v>
       </c>
       <c r="B281" t="s">
-        <v>635</v>
+        <v>715</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -7031,10 +8282,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>636</v>
+        <v>716</v>
       </c>
       <c r="B282" t="s">
-        <v>637</v>
+        <v>717</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -7045,10 +8296,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>638</v>
+        <v>718</v>
       </c>
       <c r="B283" t="s">
-        <v>639</v>
+        <v>719</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -7059,10 +8310,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>640</v>
+        <v>720</v>
       </c>
       <c r="B284" t="s">
-        <v>641</v>
+        <v>721</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -7073,10 +8324,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>642</v>
+        <v>722</v>
       </c>
       <c r="B285" t="s">
-        <v>643</v>
+        <v>723</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -7087,10 +8338,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>644</v>
+        <v>724</v>
       </c>
       <c r="B286" t="s">
-        <v>645</v>
+        <v>725</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -7101,10 +8352,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>646</v>
+        <v>726</v>
       </c>
       <c r="B287" t="s">
-        <v>647</v>
+        <v>727</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -7115,10 +8366,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>648</v>
+        <v>728</v>
       </c>
       <c r="B288" t="s">
-        <v>649</v>
+        <v>729</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -7129,10 +8380,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>650</v>
+        <v>730</v>
       </c>
       <c r="B289" t="s">
-        <v>651</v>
+        <v>731</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -7143,10 +8394,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>652</v>
+        <v>732</v>
       </c>
       <c r="B290" t="s">
-        <v>653</v>
+        <v>733</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -7157,10 +8408,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>654</v>
+        <v>734</v>
       </c>
       <c r="B291" t="s">
-        <v>655</v>
+        <v>735</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -7171,24 +8422,42 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>656</v>
+        <v>736</v>
       </c>
       <c r="B292" t="s">
-        <v>657</v>
+        <v>737</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292">
         <v>0</v>
+      </c>
+      <c r="E292" t="s">
+        <v>13</v>
+      </c>
+      <c r="G292">
+        <v>5450</v>
+      </c>
+      <c r="H292">
+        <v>3900</v>
+      </c>
+      <c r="I292" t="s">
+        <v>14</v>
+      </c>
+      <c r="J292" t="s">
+        <v>15</v>
+      </c>
+      <c r="K292" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>658</v>
+        <v>739</v>
       </c>
       <c r="B293" t="s">
-        <v>659</v>
+        <v>740</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -7199,10 +8468,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>660</v>
+        <v>741</v>
       </c>
       <c r="B294" t="s">
-        <v>661</v>
+        <v>742</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -7213,10 +8482,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>662</v>
+        <v>743</v>
       </c>
       <c r="B295" t="s">
-        <v>663</v>
+        <v>744</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -7227,10 +8496,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>664</v>
+        <v>745</v>
       </c>
       <c r="B296" t="s">
-        <v>665</v>
+        <v>746</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -7241,10 +8510,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>666</v>
+        <v>747</v>
       </c>
       <c r="B297" t="s">
-        <v>667</v>
+        <v>748</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -7255,10 +8524,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>668</v>
+        <v>749</v>
       </c>
       <c r="B298" t="s">
-        <v>669</v>
+        <v>750</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -7269,24 +8538,42 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>670</v>
+        <v>751</v>
       </c>
       <c r="B299" t="s">
-        <v>671</v>
+        <v>752</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299">
         <v>0</v>
+      </c>
+      <c r="E299" t="s">
+        <v>13</v>
+      </c>
+      <c r="G299">
+        <v>5850</v>
+      </c>
+      <c r="H299">
+        <v>4500</v>
+      </c>
+      <c r="I299" t="s">
+        <v>14</v>
+      </c>
+      <c r="J299" t="s">
+        <v>15</v>
+      </c>
+      <c r="K299" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>672</v>
+        <v>754</v>
       </c>
       <c r="B300" t="s">
-        <v>673</v>
+        <v>755</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -7297,10 +8584,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>674</v>
+        <v>756</v>
       </c>
       <c r="B301" t="s">
-        <v>675</v>
+        <v>757</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -7311,10 +8598,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>676</v>
+        <v>758</v>
       </c>
       <c r="B302" t="s">
-        <v>677</v>
+        <v>759</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -7325,10 +8612,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>678</v>
+        <v>760</v>
       </c>
       <c r="B303" t="s">
-        <v>679</v>
+        <v>761</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -7339,10 +8626,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>680</v>
+        <v>762</v>
       </c>
       <c r="B304" t="s">
-        <v>681</v>
+        <v>763</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -7353,24 +8640,42 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>682</v>
+        <v>764</v>
       </c>
       <c r="B305" t="s">
-        <v>683</v>
+        <v>765</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305">
         <v>0</v>
+      </c>
+      <c r="E305" t="s">
+        <v>13</v>
+      </c>
+      <c r="G305">
+        <v>5800</v>
+      </c>
+      <c r="H305">
+        <v>4650</v>
+      </c>
+      <c r="I305" t="s">
+        <v>14</v>
+      </c>
+      <c r="J305" t="s">
+        <v>15</v>
+      </c>
+      <c r="K305" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>684</v>
+        <v>767</v>
       </c>
       <c r="B306" t="s">
-        <v>685</v>
+        <v>768</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -7381,10 +8686,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>686</v>
+        <v>769</v>
       </c>
       <c r="B307" t="s">
-        <v>687</v>
+        <v>770</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -7395,10 +8700,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>688</v>
+        <v>771</v>
       </c>
       <c r="B308" t="s">
-        <v>689</v>
+        <v>772</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -7409,10 +8714,10 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>690</v>
+        <v>773</v>
       </c>
       <c r="B309" t="s">
-        <v>691</v>
+        <v>774</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -7423,10 +8728,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>692</v>
+        <v>775</v>
       </c>
       <c r="B310" t="s">
-        <v>693</v>
+        <v>776</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -7437,10 +8742,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>694</v>
+        <v>777</v>
       </c>
       <c r="B311" t="s">
-        <v>695</v>
+        <v>778</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -7451,52 +8756,82 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>696</v>
+        <v>779</v>
       </c>
       <c r="B312" t="s">
-        <v>697</v>
+        <v>780</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312">
         <v>0</v>
+      </c>
+      <c r="K312" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>698</v>
+        <v>782</v>
       </c>
       <c r="B313" t="s">
-        <v>699</v>
+        <v>783</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313">
         <v>0</v>
+      </c>
+      <c r="E313" t="s">
+        <v>13</v>
+      </c>
+      <c r="G313">
+        <v>6000</v>
+      </c>
+      <c r="H313">
+        <v>4600</v>
+      </c>
+      <c r="I313" t="s">
+        <v>14</v>
+      </c>
+      <c r="J313" t="s">
+        <v>15</v>
+      </c>
+      <c r="K313" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>700</v>
+        <v>785</v>
       </c>
       <c r="B314" t="s">
-        <v>701</v>
+        <v>786</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314">
         <v>0</v>
+      </c>
+      <c r="E314" t="s">
+        <v>19</v>
+      </c>
+      <c r="F314" t="s">
+        <v>24</v>
+      </c>
+      <c r="K314" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>702</v>
+        <v>788</v>
       </c>
       <c r="B315" t="s">
-        <v>703</v>
+        <v>789</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -7507,10 +8842,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>704</v>
+        <v>790</v>
       </c>
       <c r="B316" t="s">
-        <v>705</v>
+        <v>791</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -7521,10 +8856,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>706</v>
+        <v>792</v>
       </c>
       <c r="B317" t="s">
-        <v>707</v>
+        <v>793</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -7535,10 +8870,10 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>708</v>
+        <v>794</v>
       </c>
       <c r="B318" t="s">
-        <v>709</v>
+        <v>795</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -7549,24 +8884,33 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>710</v>
+        <v>796</v>
       </c>
       <c r="B319" t="s">
-        <v>711</v>
+        <v>797</v>
       </c>
       <c r="C319">
         <v>1</v>
       </c>
       <c r="D319">
         <v>0</v>
+      </c>
+      <c r="E319" t="s">
+        <v>19</v>
+      </c>
+      <c r="F319" t="s">
+        <v>24</v>
+      </c>
+      <c r="K319" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>712</v>
+        <v>798</v>
       </c>
       <c r="B320" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -7577,10 +8921,10 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>714</v>
+        <v>800</v>
       </c>
       <c r="B321" t="s">
-        <v>715</v>
+        <v>801</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -7591,10 +8935,10 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>716</v>
+        <v>802</v>
       </c>
       <c r="B322" t="s">
-        <v>717</v>
+        <v>803</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -7605,10 +8949,10 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>718</v>
+        <v>804</v>
       </c>
       <c r="B323" t="s">
-        <v>719</v>
+        <v>805</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -7619,24 +8963,33 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>720</v>
+        <v>806</v>
       </c>
       <c r="B324" t="s">
-        <v>721</v>
+        <v>807</v>
       </c>
       <c r="C324">
         <v>1</v>
       </c>
       <c r="D324">
         <v>0</v>
+      </c>
+      <c r="E324" t="s">
+        <v>19</v>
+      </c>
+      <c r="F324" t="s">
+        <v>85</v>
+      </c>
+      <c r="K324" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>722</v>
+        <v>809</v>
       </c>
       <c r="B325" t="s">
-        <v>723</v>
+        <v>810</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -7647,10 +9000,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>724</v>
+        <v>811</v>
       </c>
       <c r="B326" t="s">
-        <v>725</v>
+        <v>812</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -7661,10 +9014,10 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>726</v>
+        <v>813</v>
       </c>
       <c r="B327" t="s">
-        <v>727</v>
+        <v>814</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -7675,24 +9028,27 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>728</v>
+        <v>815</v>
       </c>
       <c r="B328" t="s">
-        <v>729</v>
+        <v>816</v>
       </c>
       <c r="C328">
         <v>1</v>
       </c>
       <c r="D328">
         <v>0</v>
+      </c>
+      <c r="K328" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>730</v>
+        <v>818</v>
       </c>
       <c r="B329" t="s">
-        <v>731</v>
+        <v>819</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -7703,10 +9059,10 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>732</v>
+        <v>820</v>
       </c>
       <c r="B330" t="s">
-        <v>733</v>
+        <v>821</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -7717,10 +9073,10 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>734</v>
+        <v>822</v>
       </c>
       <c r="B331" t="s">
-        <v>735</v>
+        <v>823</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -7731,10 +9087,10 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>736</v>
+        <v>824</v>
       </c>
       <c r="B332" t="s">
-        <v>737</v>
+        <v>825</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -7745,10 +9101,10 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>738</v>
+        <v>826</v>
       </c>
       <c r="B333" t="s">
-        <v>739</v>
+        <v>827</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -7759,10 +9115,10 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>740</v>
+        <v>828</v>
       </c>
       <c r="B334" t="s">
-        <v>741</v>
+        <v>829</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -7773,10 +9129,10 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>742</v>
+        <v>830</v>
       </c>
       <c r="B335" t="s">
-        <v>743</v>
+        <v>831</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -7787,10 +9143,10 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>744</v>
+        <v>832</v>
       </c>
       <c r="B336" t="s">
-        <v>745</v>
+        <v>833</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -7801,10 +9157,10 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>746</v>
+        <v>834</v>
       </c>
       <c r="B337" t="s">
-        <v>747</v>
+        <v>835</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -7815,10 +9171,10 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>748</v>
+        <v>836</v>
       </c>
       <c r="B338" t="s">
-        <v>749</v>
+        <v>837</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -7829,10 +9185,10 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>750</v>
+        <v>838</v>
       </c>
       <c r="B339" t="s">
-        <v>751</v>
+        <v>839</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -7843,10 +9199,10 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>752</v>
+        <v>840</v>
       </c>
       <c r="B340" t="s">
-        <v>753</v>
+        <v>841</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -7857,38 +9213,65 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>754</v>
+        <v>842</v>
       </c>
       <c r="B341" t="s">
-        <v>755</v>
+        <v>843</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341">
         <v>0</v>
+      </c>
+      <c r="E341" t="s">
+        <v>13</v>
+      </c>
+      <c r="G341">
+        <v>6450</v>
+      </c>
+      <c r="H341">
+        <v>3750</v>
+      </c>
+      <c r="I341" t="s">
+        <v>14</v>
+      </c>
+      <c r="J341" t="s">
+        <v>29</v>
+      </c>
+      <c r="K341" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>756</v>
+        <v>845</v>
       </c>
       <c r="B342" t="s">
-        <v>757</v>
+        <v>846</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342">
         <v>0</v>
+      </c>
+      <c r="E342" t="s">
+        <v>19</v>
+      </c>
+      <c r="F342" t="s">
+        <v>847</v>
+      </c>
+      <c r="K342" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>758</v>
+        <v>849</v>
       </c>
       <c r="B343" t="s">
-        <v>759</v>
+        <v>850</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -7899,24 +9282,33 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>760</v>
+        <v>851</v>
       </c>
       <c r="B344" t="s">
-        <v>761</v>
+        <v>852</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344">
         <v>0</v>
+      </c>
+      <c r="E344" t="s">
+        <v>19</v>
+      </c>
+      <c r="F344" t="s">
+        <v>853</v>
+      </c>
+      <c r="K344" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>762</v>
+        <v>855</v>
       </c>
       <c r="B345" t="s">
-        <v>763</v>
+        <v>856</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -7927,10 +9319,10 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>764</v>
+        <v>857</v>
       </c>
       <c r="B346" t="s">
-        <v>765</v>
+        <v>858</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -7941,10 +9333,10 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>766</v>
+        <v>859</v>
       </c>
       <c r="B347" t="s">
-        <v>767</v>
+        <v>860</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -7955,10 +9347,10 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>768</v>
+        <v>861</v>
       </c>
       <c r="B348" t="s">
-        <v>769</v>
+        <v>862</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -7969,10 +9361,10 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>770</v>
+        <v>863</v>
       </c>
       <c r="B349" t="s">
-        <v>771</v>
+        <v>864</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -7983,10 +9375,10 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>772</v>
+        <v>865</v>
       </c>
       <c r="B350" t="s">
-        <v>773</v>
+        <v>866</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -7997,10 +9389,10 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>774</v>
+        <v>867</v>
       </c>
       <c r="B351" t="s">
-        <v>775</v>
+        <v>868</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -8011,10 +9403,10 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>776</v>
+        <v>869</v>
       </c>
       <c r="B352" t="s">
-        <v>777</v>
+        <v>870</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -8025,10 +9417,10 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>778</v>
+        <v>871</v>
       </c>
       <c r="B353" t="s">
-        <v>779</v>
+        <v>872</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -8039,10 +9431,10 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>780</v>
+        <v>873</v>
       </c>
       <c r="B354" t="s">
-        <v>781</v>
+        <v>874</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -8053,10 +9445,10 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>782</v>
+        <v>875</v>
       </c>
       <c r="B355" t="s">
-        <v>783</v>
+        <v>876</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -8067,10 +9459,10 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>784</v>
+        <v>877</v>
       </c>
       <c r="B356" t="s">
-        <v>785</v>
+        <v>878</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -8081,24 +9473,42 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>786</v>
+        <v>879</v>
       </c>
       <c r="B357" t="s">
-        <v>787</v>
+        <v>880</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357">
         <v>0</v>
+      </c>
+      <c r="E357" t="s">
+        <v>13</v>
+      </c>
+      <c r="G357">
+        <v>1580</v>
+      </c>
+      <c r="H357">
+        <v>1240</v>
+      </c>
+      <c r="I357" t="s">
+        <v>93</v>
+      </c>
+      <c r="J357" t="s">
+        <v>15</v>
+      </c>
+      <c r="K357" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>788</v>
+        <v>882</v>
       </c>
       <c r="B358" t="s">
-        <v>789</v>
+        <v>883</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -8109,10 +9519,10 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>790</v>
+        <v>884</v>
       </c>
       <c r="B359" t="s">
-        <v>791</v>
+        <v>885</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -8123,10 +9533,10 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>792</v>
+        <v>886</v>
       </c>
       <c r="B360" t="s">
-        <v>793</v>
+        <v>887</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -8137,10 +9547,10 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>794</v>
+        <v>888</v>
       </c>
       <c r="B361" t="s">
-        <v>795</v>
+        <v>889</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -8151,10 +9561,10 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>796</v>
+        <v>890</v>
       </c>
       <c r="B362" t="s">
-        <v>797</v>
+        <v>891</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -8165,10 +9575,10 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>798</v>
+        <v>892</v>
       </c>
       <c r="B363" t="s">
-        <v>799</v>
+        <v>893</v>
       </c>
       <c r="C363">
         <v>1</v>
@@ -8179,10 +9589,10 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>800</v>
+        <v>894</v>
       </c>
       <c r="B364" t="s">
-        <v>801</v>
+        <v>895</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -8205,10 +9615,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>802</v>
+        <v>896</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>803</v>
+        <v>897</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>

--- a/scripts/seed-data/source/map-worlds-curation.xlsx
+++ b/scripts/seed-data/source/map-worlds-curation.xlsx
@@ -263,180 +263,189 @@
     <t>Luna</t>
   </si>
   <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Civilized World</t>
+  </si>
+  <si>
+    <t>Sol-System; eigener Pin seit Great Journeys (Garro/Great Crusade) - vorher rollup zu terra</t>
+  </si>
+  <si>
+    <t>medrengard</t>
+  </si>
+  <si>
+    <t>Medrengard</t>
+  </si>
+  <si>
+    <t>eye-of-terror</t>
+  </si>
+  <si>
+    <t>Daemon-Welt im Eye</t>
+  </si>
+  <si>
+    <t>planet_of_the_sorcerers</t>
+  </si>
+  <si>
+    <t>Planet of the Sorcerers</t>
+  </si>
+  <si>
+    <t>prospero</t>
+  </si>
+  <si>
+    <t>seit 999.M41 über Prospero (Wrath of Magnus); Alternative eye-of-terror — Philipp entscheidet im Review</t>
+  </si>
+  <si>
+    <t>scarus</t>
+  </si>
+  <si>
+    <t>Scarus Sector</t>
+  </si>
+  <si>
+    <t>Obscurus</t>
+  </si>
+  <si>
+    <t>mittel (relativ); Anker Eustis Majoris(1605/1225) — Redditor verortet den Eisenhorn-Raum dort</t>
+  </si>
+  <si>
+    <t>vengeful_spirit</t>
+  </si>
+  <si>
+    <t>Vengeful Spirit</t>
+  </si>
+  <si>
+    <t>Abaddons Flaggschiff, M41/42-Basis Eye (Philipp 2026-07-02: Schiffe mitnehmen)</t>
+  </si>
+  <si>
+    <t>cryptus</t>
+  </si>
+  <si>
+    <t>Cryptus-System</t>
+  </si>
+  <si>
+    <t>mittel; Schildsystem Baals (Red Scar)</t>
+  </si>
+  <si>
+    <t>eastern_fringe</t>
+  </si>
+  <si>
+    <t>Eastern Fringe</t>
+  </si>
+  <si>
+    <t>mittel; Ostrand der Karte — grobe Regions-Markierung</t>
+  </si>
+  <si>
+    <t>pariah_nexus</t>
+  </si>
+  <si>
+    <t>Pariah Nexus</t>
+  </si>
+  <si>
+    <t>niedrig; Nephilim-Sektor, Ultima (Lexicanum) — grobe Verortung</t>
+  </si>
+  <si>
+    <t>spire</t>
+  </si>
+  <si>
+    <t>The Spire</t>
+  </si>
+  <si>
+    <t>⚠ prüfen: falls „The Spire“-Bücher nicht Necromunda-Korpus sind, Aktion leer lassen + im Report vermerken — geprüft (CC, Brief 183): alle 5 Bücher mit dieser Location sind Necromunda-Serie</t>
+  </si>
+  <si>
+    <t>tizca</t>
+  </si>
+  <si>
+    <t>Tizca</t>
+  </si>
+  <si>
+    <t>Stadt auf Prospero</t>
+  </si>
+  <si>
+    <t>black_library_place</t>
+  </si>
+  <si>
+    <t>Black Library</t>
+  </si>
+  <si>
+    <t>the-black-library</t>
+  </si>
+  <si>
+    <t>identisches Objekt</t>
+  </si>
+  <si>
+    <t>candleworld</t>
+  </si>
+  <si>
+    <t>Candleworld</t>
+  </si>
+  <si>
+    <t>ghoul_stars</t>
+  </si>
+  <si>
+    <t>Ghoul Stars</t>
+  </si>
+  <si>
+    <t>niedrig; NO-Rand</t>
+  </si>
+  <si>
+    <t>gothic_sector</t>
+  </si>
+  <si>
+    <t>Gothic Sector</t>
+  </si>
+  <si>
+    <t>niedrig-mittel; Obscurus-Nord an der Ultima-Grenze</t>
+  </si>
+  <si>
+    <t>helican</t>
+  </si>
+  <si>
+    <t>Helican Subsector</t>
+  </si>
+  <si>
+    <t>gudrun</t>
+  </si>
+  <si>
+    <t>Gudrun = Hauptwelt des Helican-Subsektors (Pin aus C)</t>
+  </si>
+  <si>
+    <t>iax</t>
+  </si>
+  <si>
+    <t>Iax</t>
+  </si>
+  <si>
+    <t>mittel; Ultramar — zwischen Calth(6398/4957) und Macragge</t>
+  </si>
+  <si>
+    <t>monarchia</t>
+  </si>
+  <si>
+    <t>Monarchia</t>
+  </si>
+  <si>
+    <t>khur</t>
+  </si>
+  <si>
+    <t>Stadt auf Khur</t>
+  </si>
+  <si>
+    <t>orath</t>
+  </si>
+  <si>
+    <t>Orath</t>
+  </si>
+  <si>
+    <t>pluto</t>
+  </si>
+  <si>
+    <t>Pluto</t>
+  </si>
+  <si>
     <t>Sol-System</t>
   </si>
   <si>
-    <t>medrengard</t>
-  </si>
-  <si>
-    <t>Medrengard</t>
-  </si>
-  <si>
-    <t>eye-of-terror</t>
-  </si>
-  <si>
-    <t>Daemon-Welt im Eye</t>
-  </si>
-  <si>
-    <t>planet_of_the_sorcerers</t>
-  </si>
-  <si>
-    <t>Planet of the Sorcerers</t>
-  </si>
-  <si>
-    <t>prospero</t>
-  </si>
-  <si>
-    <t>seit 999.M41 über Prospero (Wrath of Magnus); Alternative eye-of-terror — Philipp entscheidet im Review</t>
-  </si>
-  <si>
-    <t>scarus</t>
-  </si>
-  <si>
-    <t>Scarus Sector</t>
-  </si>
-  <si>
-    <t>Obscurus</t>
-  </si>
-  <si>
-    <t>mittel (relativ); Anker Eustis Majoris(1605/1225) — Redditor verortet den Eisenhorn-Raum dort</t>
-  </si>
-  <si>
-    <t>vengeful_spirit</t>
-  </si>
-  <si>
-    <t>Vengeful Spirit</t>
-  </si>
-  <si>
-    <t>Abaddons Flaggschiff, M41/42-Basis Eye (Philipp 2026-07-02: Schiffe mitnehmen)</t>
-  </si>
-  <si>
-    <t>cryptus</t>
-  </si>
-  <si>
-    <t>Cryptus-System</t>
-  </si>
-  <si>
-    <t>mittel; Schildsystem Baals (Red Scar)</t>
-  </si>
-  <si>
-    <t>eastern_fringe</t>
-  </si>
-  <si>
-    <t>Eastern Fringe</t>
-  </si>
-  <si>
-    <t>mittel; Ostrand der Karte — grobe Regions-Markierung</t>
-  </si>
-  <si>
-    <t>pariah_nexus</t>
-  </si>
-  <si>
-    <t>Pariah Nexus</t>
-  </si>
-  <si>
-    <t>niedrig; Nephilim-Sektor, Ultima (Lexicanum) — grobe Verortung</t>
-  </si>
-  <si>
-    <t>spire</t>
-  </si>
-  <si>
-    <t>The Spire</t>
-  </si>
-  <si>
-    <t>⚠ prüfen: falls „The Spire“-Bücher nicht Necromunda-Korpus sind, Aktion leer lassen + im Report vermerken — geprüft (CC, Brief 183): alle 5 Bücher mit dieser Location sind Necromunda-Serie</t>
-  </si>
-  <si>
-    <t>tizca</t>
-  </si>
-  <si>
-    <t>Tizca</t>
-  </si>
-  <si>
-    <t>Stadt auf Prospero</t>
-  </si>
-  <si>
-    <t>black_library_place</t>
-  </si>
-  <si>
-    <t>Black Library</t>
-  </si>
-  <si>
-    <t>the-black-library</t>
-  </si>
-  <si>
-    <t>identisches Objekt</t>
-  </si>
-  <si>
-    <t>candleworld</t>
-  </si>
-  <si>
-    <t>Candleworld</t>
-  </si>
-  <si>
-    <t>ghoul_stars</t>
-  </si>
-  <si>
-    <t>Ghoul Stars</t>
-  </si>
-  <si>
-    <t>niedrig; NO-Rand</t>
-  </si>
-  <si>
-    <t>gothic_sector</t>
-  </si>
-  <si>
-    <t>Gothic Sector</t>
-  </si>
-  <si>
-    <t>niedrig-mittel; Obscurus-Nord an der Ultima-Grenze</t>
-  </si>
-  <si>
-    <t>helican</t>
-  </si>
-  <si>
-    <t>Helican Subsector</t>
-  </si>
-  <si>
-    <t>gudrun</t>
-  </si>
-  <si>
-    <t>Gudrun = Hauptwelt des Helican-Subsektors (Pin aus C)</t>
-  </si>
-  <si>
-    <t>iax</t>
-  </si>
-  <si>
-    <t>Iax</t>
-  </si>
-  <si>
-    <t>mittel; Ultramar — zwischen Calth(6398/4957) und Macragge</t>
-  </si>
-  <si>
-    <t>monarchia</t>
-  </si>
-  <si>
-    <t>Monarchia</t>
-  </si>
-  <si>
-    <t>khur</t>
-  </si>
-  <si>
-    <t>Stadt auf Khur</t>
-  </si>
-  <si>
-    <t>orath</t>
-  </si>
-  <si>
-    <t>Orath</t>
-  </si>
-  <si>
-    <t>pluto</t>
-  </si>
-  <si>
-    <t>Pluto</t>
-  </si>
-  <si>
     <t>sancour</t>
   </si>
   <si>
@@ -465,9 +474,6 @@
   </si>
   <si>
     <t>Alaxxes Nebula</t>
-  </si>
-  <si>
-    <t>Solar</t>
   </si>
   <si>
     <t>niedrig; Nebel nahe Fenris (Legacy of Russ)</t>
@@ -3299,21 +3305,30 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="G21">
+        <v>2370</v>
+      </c>
+      <c r="H21">
+        <v>3324</v>
+      </c>
+      <c r="I21" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s">
+        <v>83</v>
       </c>
       <c r="K21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -3325,18 +3340,18 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -3348,18 +3363,18 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -3377,21 +3392,21 @@
         <v>1288</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J24" t="s">
         <v>29</v>
       </c>
       <c r="K24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C25">
         <v>7</v>
@@ -3403,18 +3418,18 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -3438,15 +3453,15 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -3470,15 +3485,15 @@
         <v>29</v>
       </c>
       <c r="K27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -3502,15 +3517,15 @@
         <v>29</v>
       </c>
       <c r="K28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -3525,15 +3540,15 @@
         <v>33</v>
       </c>
       <c r="K29" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -3545,18 +3560,18 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -3568,18 +3583,18 @@
         <v>57</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C32">
         <v>4</v>
@@ -3590,10 +3605,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -3617,15 +3632,15 @@
         <v>29</v>
       </c>
       <c r="K33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -3643,21 +3658,21 @@
         <v>1745</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J34" t="s">
         <v>29</v>
       </c>
       <c r="K34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -3669,18 +3684,18 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -3704,15 +3719,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -3724,18 +3739,18 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K37" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -3746,10 +3761,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -3764,15 +3779,15 @@
         <v>24</v>
       </c>
       <c r="K39" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C40">
         <v>4</v>
@@ -3790,21 +3805,21 @@
         <v>1372</v>
       </c>
       <c r="I40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J40" t="s">
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -3828,15 +3843,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -3847,10 +3862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -3868,21 +3883,21 @@
         <v>2250</v>
       </c>
       <c r="I43" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s">
         <v>29</v>
       </c>
       <c r="K43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -3893,10 +3908,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -3911,15 +3926,15 @@
         <v>51</v>
       </c>
       <c r="K45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3931,18 +3946,18 @@
         <v>57</v>
       </c>
       <c r="F46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -3954,18 +3969,18 @@
         <v>57</v>
       </c>
       <c r="F47" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -3977,18 +3992,18 @@
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -4012,15 +4027,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -4038,21 +4053,21 @@
         <v>1344</v>
       </c>
       <c r="I50" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J50" t="s">
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -4063,10 +4078,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -4081,15 +4096,15 @@
         <v>24</v>
       </c>
       <c r="K52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B53" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -4107,21 +4122,21 @@
         <v>1253</v>
       </c>
       <c r="I53" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J53" t="s">
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -4145,15 +4160,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B55" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -4177,15 +4192,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B56" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C56">
         <v>3</v>
@@ -4196,10 +4211,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B57" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -4210,10 +4225,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C58">
         <v>3</v>
@@ -4237,15 +4252,15 @@
         <v>29</v>
       </c>
       <c r="K58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B59" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -4269,15 +4284,15 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -4295,21 +4310,21 @@
         <v>1991</v>
       </c>
       <c r="I60" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J60" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K60" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B61" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -4320,10 +4335,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C62">
         <v>3</v>
@@ -4347,15 +4362,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -4366,10 +4381,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -4393,15 +4408,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -4425,15 +4440,15 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B66" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -4444,10 +4459,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -4471,15 +4486,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -4490,10 +4505,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B69" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -4505,18 +4520,18 @@
         <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K69" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B70" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -4540,15 +4555,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -4572,15 +4587,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -4591,10 +4606,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B73" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -4605,10 +4620,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C74">
         <v>2</v>
@@ -4619,10 +4634,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -4634,18 +4649,18 @@
         <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K75" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -4656,10 +4671,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B77" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C77">
         <v>2</v>
@@ -4670,10 +4685,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -4684,10 +4699,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -4698,10 +4713,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -4712,10 +4727,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -4739,15 +4754,15 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -4758,10 +4773,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B83" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -4773,18 +4788,18 @@
         <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K83" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -4795,10 +4810,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -4810,18 +4825,18 @@
         <v>19</v>
       </c>
       <c r="F85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K85" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B86" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -4832,10 +4847,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B87" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -4846,10 +4861,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B88" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -4864,15 +4879,15 @@
         <v>24</v>
       </c>
       <c r="K88" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B89" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -4884,18 +4899,18 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K89" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B90" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -4919,15 +4934,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B91" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -4938,10 +4953,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B92" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -4952,10 +4967,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B93" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -4973,21 +4988,21 @@
         <v>2450</v>
       </c>
       <c r="I93" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="J93" t="s">
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B94" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -4998,10 +5013,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B95" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -5025,15 +5040,15 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B96" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -5057,15 +5072,15 @@
         <v>15</v>
       </c>
       <c r="K96" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B97" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -5076,10 +5091,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B98" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -5091,18 +5106,18 @@
         <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K98" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B99" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -5113,10 +5128,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B100" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -5127,10 +5142,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B101" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C101">
         <v>2</v>
@@ -5148,21 +5163,21 @@
         <v>1310</v>
       </c>
       <c r="I101" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J101" t="s">
         <v>15</v>
       </c>
       <c r="K101" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B102" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -5173,10 +5188,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B103" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C103">
         <v>2</v>
@@ -5187,10 +5202,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B104" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -5201,10 +5216,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B105" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C105">
         <v>2</v>
@@ -5215,10 +5230,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B106" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -5242,15 +5257,15 @@
         <v>15</v>
       </c>
       <c r="K106" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B107" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -5265,15 +5280,15 @@
         <v>24</v>
       </c>
       <c r="K107" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -5291,21 +5306,21 @@
         <v>2250</v>
       </c>
       <c r="I108" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J108" t="s">
         <v>15</v>
       </c>
       <c r="K108" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B109" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C109">
         <v>2</v>
@@ -5316,10 +5331,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B110" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C110">
         <v>2</v>
@@ -5330,10 +5345,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B111" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -5344,10 +5359,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B112" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -5358,10 +5373,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B113" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -5372,10 +5387,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B114" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -5386,10 +5401,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B115" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -5400,10 +5415,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B116" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -5427,15 +5442,15 @@
         <v>15</v>
       </c>
       <c r="K116" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -5459,15 +5474,15 @@
         <v>15</v>
       </c>
       <c r="K117" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -5478,10 +5493,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -5492,10 +5507,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B120" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -5506,10 +5521,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -5521,18 +5536,18 @@
         <v>19</v>
       </c>
       <c r="F121" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K121" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B122" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -5556,15 +5571,15 @@
         <v>15</v>
       </c>
       <c r="K122" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B123" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -5579,15 +5594,15 @@
         <v>67</v>
       </c>
       <c r="K123" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -5598,10 +5613,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B125" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -5613,18 +5628,18 @@
         <v>57</v>
       </c>
       <c r="F125" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K125" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B126" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -5635,10 +5650,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B127" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -5662,15 +5677,15 @@
         <v>15</v>
       </c>
       <c r="K127" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B128" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -5681,10 +5696,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B129" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -5696,18 +5711,18 @@
         <v>19</v>
       </c>
       <c r="F129" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K129" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B130" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -5718,10 +5733,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -5732,10 +5747,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B132" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C132">
         <v>2</v>
@@ -5746,10 +5761,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B133" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -5773,15 +5788,15 @@
         <v>15</v>
       </c>
       <c r="K133" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B134" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -5792,10 +5807,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B135" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C135">
         <v>2</v>
@@ -5806,10 +5821,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B136" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -5820,10 +5835,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B137" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C137">
         <v>2</v>
@@ -5832,15 +5847,15 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B138" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C138">
         <v>2</v>
@@ -5851,10 +5866,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B139" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C139">
         <v>2</v>
@@ -5866,18 +5881,18 @@
         <v>19</v>
       </c>
       <c r="F139" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K139" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B140" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C140">
         <v>2</v>
@@ -5888,10 +5903,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B141" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C141">
         <v>2</v>
@@ -5900,15 +5915,15 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B142" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C142">
         <v>2</v>
@@ -5919,10 +5934,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B143" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C143">
         <v>2</v>
@@ -5933,10 +5948,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B144" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C144">
         <v>2</v>
@@ -5960,15 +5975,15 @@
         <v>15</v>
       </c>
       <c r="K144" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B145" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C145">
         <v>2</v>
@@ -5979,10 +5994,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B146" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5997,15 +6012,15 @@
         <v>24</v>
       </c>
       <c r="K146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C147">
         <v>2</v>
@@ -6016,10 +6031,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B148" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C148">
         <v>2</v>
@@ -6030,10 +6045,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B149" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C149">
         <v>2</v>
@@ -6044,10 +6059,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B150" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -6059,18 +6074,18 @@
         <v>19</v>
       </c>
       <c r="F150" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B151" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C151">
         <v>2</v>
@@ -6081,10 +6096,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B152" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C152">
         <v>2</v>
@@ -6102,21 +6117,21 @@
         <v>1330</v>
       </c>
       <c r="I152" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J152" t="s">
         <v>15</v>
       </c>
       <c r="K152" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B153" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -6127,10 +6142,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B154" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -6141,10 +6156,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B155" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -6155,10 +6170,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B156" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -6169,10 +6184,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B157" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -6187,15 +6202,15 @@
         <v>24</v>
       </c>
       <c r="K157" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B158" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -6206,10 +6221,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B159" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -6220,10 +6235,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B160" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -6234,10 +6249,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B161" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -6248,10 +6263,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B162" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -6262,10 +6277,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B163" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6277,18 +6292,18 @@
         <v>19</v>
       </c>
       <c r="F163" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K163" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B164" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -6299,10 +6314,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B165" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -6313,10 +6328,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B166" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -6327,10 +6342,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B167" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -6341,10 +6356,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B168" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -6355,10 +6370,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B169" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -6369,10 +6384,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B170" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -6383,10 +6398,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B171" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -6397,10 +6412,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B172" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -6411,10 +6426,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B173" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -6425,10 +6440,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B174" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -6446,21 +6461,21 @@
         <v>1100</v>
       </c>
       <c r="I174" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J174" t="s">
         <v>29</v>
       </c>
       <c r="K174" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B175" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -6484,15 +6499,15 @@
         <v>15</v>
       </c>
       <c r="K175" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B176" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6503,10 +6518,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B177" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6515,15 +6530,15 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B178" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6534,10 +6549,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B179" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6548,10 +6563,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B180" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -6562,10 +6577,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B181" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -6576,10 +6591,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B182" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6590,10 +6605,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B183" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6605,18 +6620,18 @@
         <v>19</v>
       </c>
       <c r="F183" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K183" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B184" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -6627,10 +6642,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B185" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -6641,10 +6656,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B186" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6655,10 +6670,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B187" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -6669,10 +6684,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B188" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -6690,21 +6705,21 @@
         <v>1400</v>
       </c>
       <c r="I188" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J188" t="s">
         <v>15</v>
       </c>
       <c r="K188" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B189" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -6715,10 +6730,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B190" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -6729,10 +6744,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B191" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -6747,15 +6762,15 @@
         <v>24</v>
       </c>
       <c r="K191" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B192" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -6766,10 +6781,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B193" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6780,10 +6795,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B194" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -6794,10 +6809,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B195" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -6808,10 +6823,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B196" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -6822,10 +6837,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B197" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -6836,10 +6851,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B198" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -6850,10 +6865,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B199" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -6864,10 +6879,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B200" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -6878,10 +6893,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B201" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -6892,10 +6907,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B202" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -6906,10 +6921,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B203" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -6927,21 +6942,21 @@
         <v>1300</v>
       </c>
       <c r="I203" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J203" t="s">
         <v>15</v>
       </c>
       <c r="K203" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B204" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -6952,10 +6967,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B205" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -6973,21 +6988,21 @@
         <v>1370</v>
       </c>
       <c r="I205" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J205" t="s">
         <v>15</v>
       </c>
       <c r="K205" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B206" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -7011,15 +7026,15 @@
         <v>29</v>
       </c>
       <c r="K206" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B207" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -7030,10 +7045,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B208" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -7042,15 +7057,15 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B209" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -7065,15 +7080,15 @@
         <v>24</v>
       </c>
       <c r="K209" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B210" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -7084,10 +7099,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B211" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -7098,10 +7113,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B212" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -7116,15 +7131,15 @@
         <v>33</v>
       </c>
       <c r="K212" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B213" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -7135,10 +7150,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B214" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -7149,10 +7164,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B215" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -7163,10 +7178,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B216" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -7177,10 +7192,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B217" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -7191,10 +7206,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B218" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -7205,10 +7220,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B219" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -7219,10 +7234,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B220" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -7233,10 +7248,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B221" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -7247,10 +7262,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B222" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -7261,10 +7276,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B223" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -7275,10 +7290,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B224" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -7289,10 +7304,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B225" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -7303,10 +7318,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B226" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -7330,15 +7345,15 @@
         <v>15</v>
       </c>
       <c r="K226" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B227" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -7353,15 +7368,15 @@
         <v>24</v>
       </c>
       <c r="K227" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B228" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -7372,10 +7387,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B229" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -7399,15 +7414,15 @@
         <v>15</v>
       </c>
       <c r="K229" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B230" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -7418,10 +7433,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B231" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -7436,15 +7451,15 @@
         <v>24</v>
       </c>
       <c r="K231" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B232" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -7462,21 +7477,21 @@
         <v>700</v>
       </c>
       <c r="I232" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J232" t="s">
         <v>29</v>
       </c>
       <c r="K232" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B233" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -7487,10 +7502,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B234" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -7501,10 +7516,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B235" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -7515,10 +7530,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B236" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -7529,10 +7544,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B237" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -7543,10 +7558,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B238" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -7557,10 +7572,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B239" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -7571,10 +7586,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B240" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -7585,10 +7600,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B241" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -7599,10 +7614,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B242" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7617,15 +7632,15 @@
         <v>24</v>
       </c>
       <c r="K242" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B243" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -7636,10 +7651,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B244" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -7650,10 +7665,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B245" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -7668,15 +7683,15 @@
         <v>20</v>
       </c>
       <c r="K245" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B246" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -7691,15 +7706,15 @@
         <v>24</v>
       </c>
       <c r="K246" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B247" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -7708,15 +7723,15 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B248" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -7725,15 +7740,15 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B249" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -7745,18 +7760,18 @@
         <v>19</v>
       </c>
       <c r="F249" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K249" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B250" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -7767,10 +7782,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B251" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -7782,18 +7797,18 @@
         <v>19</v>
       </c>
       <c r="F251" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K251" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B252" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -7808,15 +7823,15 @@
         <v>33</v>
       </c>
       <c r="K252" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B253" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -7828,18 +7843,18 @@
         <v>19</v>
       </c>
       <c r="F253" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K253" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B254" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -7850,10 +7865,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B255" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -7864,10 +7879,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B256" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -7878,10 +7893,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B257" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -7892,10 +7907,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B258" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -7906,10 +7921,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B259" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -7920,10 +7935,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B260" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -7934,10 +7949,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B261" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -7948,10 +7963,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B262" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -7975,15 +7990,15 @@
         <v>15</v>
       </c>
       <c r="K262" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B263" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -7994,10 +8009,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B264" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8008,10 +8023,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B265" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8022,10 +8037,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B266" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8036,10 +8051,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B267" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8050,10 +8065,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B268" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8064,10 +8079,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B269" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8082,15 +8097,15 @@
         <v>20</v>
       </c>
       <c r="K269" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B270" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8101,10 +8116,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B271" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8115,10 +8130,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B272" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8129,10 +8144,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B273" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -8147,15 +8162,15 @@
         <v>24</v>
       </c>
       <c r="K273" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B274" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -8167,18 +8182,18 @@
         <v>19</v>
       </c>
       <c r="F274" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K274" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B275" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -8189,10 +8204,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B276" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -8203,10 +8218,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B277" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -8217,10 +8232,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B278" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -8231,10 +8246,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B279" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -8246,18 +8261,18 @@
         <v>19</v>
       </c>
       <c r="F279" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="K279" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B280" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -8268,10 +8283,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B281" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -8282,10 +8297,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B282" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -8296,10 +8311,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B283" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -8310,10 +8325,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B284" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -8324,10 +8339,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B285" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -8338,10 +8353,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B286" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -8352,10 +8367,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B287" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -8366,10 +8381,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B288" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -8380,10 +8395,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B289" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -8394,10 +8409,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B290" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -8408,10 +8423,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B291" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -8422,10 +8437,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B292" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -8449,15 +8464,15 @@
         <v>15</v>
       </c>
       <c r="K292" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B293" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -8468,10 +8483,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B294" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -8482,10 +8497,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B295" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -8496,10 +8511,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B296" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -8510,10 +8525,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B297" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -8524,10 +8539,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B298" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -8538,10 +8553,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B299" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -8565,15 +8580,15 @@
         <v>15</v>
       </c>
       <c r="K299" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B300" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -8584,10 +8599,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B301" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -8598,10 +8613,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B302" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -8612,10 +8627,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B303" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -8626,10 +8641,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B304" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -8640,10 +8655,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B305" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -8667,15 +8682,15 @@
         <v>15</v>
       </c>
       <c r="K305" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B306" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -8686,10 +8701,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B307" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -8700,10 +8715,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B308" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -8714,10 +8729,10 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B309" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -8728,10 +8743,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B310" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -8742,10 +8757,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B311" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -8756,10 +8771,10 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B312" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -8768,15 +8783,15 @@
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B313" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -8800,15 +8815,15 @@
         <v>15</v>
       </c>
       <c r="K313" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B314" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -8823,15 +8838,15 @@
         <v>24</v>
       </c>
       <c r="K314" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B315" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -8842,10 +8857,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B316" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -8856,10 +8871,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B317" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -8870,10 +8885,10 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B318" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -8884,10 +8899,10 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B319" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -8902,15 +8917,15 @@
         <v>24</v>
       </c>
       <c r="K319" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B320" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -8921,10 +8936,10 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B321" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -8935,10 +8950,10 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B322" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -8949,10 +8964,10 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B323" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -8963,10 +8978,10 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B324" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -8978,18 +8993,18 @@
         <v>19</v>
       </c>
       <c r="F324" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K324" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B325" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9000,10 +9015,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B326" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9014,10 +9029,10 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B327" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9028,10 +9043,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B328" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9040,15 +9055,15 @@
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B329" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9059,10 +9074,10 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B330" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9073,10 +9088,10 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B331" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9087,10 +9102,10 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B332" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9101,10 +9116,10 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B333" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9115,10 +9130,10 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B334" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9129,10 +9144,10 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B335" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9143,10 +9158,10 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B336" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9157,10 +9172,10 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B337" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9171,10 +9186,10 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B338" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9185,10 +9200,10 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B339" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9199,10 +9214,10 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B340" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9213,10 +9228,10 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B341" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9240,15 +9255,15 @@
         <v>29</v>
       </c>
       <c r="K341" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B342" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9260,18 +9275,18 @@
         <v>19</v>
       </c>
       <c r="F342" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="K342" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B343" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9282,10 +9297,10 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B344" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9297,18 +9312,18 @@
         <v>19</v>
       </c>
       <c r="F344" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="K344" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B345" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9319,10 +9334,10 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B346" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9333,10 +9348,10 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B347" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9347,10 +9362,10 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B348" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9361,10 +9376,10 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B349" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -9375,10 +9390,10 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B350" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9389,10 +9404,10 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B351" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -9403,10 +9418,10 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B352" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -9417,10 +9432,10 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B353" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -9431,10 +9446,10 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B354" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -9445,10 +9460,10 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B355" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -9459,10 +9474,10 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B356" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -9473,10 +9488,10 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B357" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -9494,21 +9509,21 @@
         <v>1240</v>
       </c>
       <c r="I357" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J357" t="s">
         <v>15</v>
       </c>
       <c r="K357" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B358" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -9519,10 +9534,10 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B359" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -9533,10 +9548,10 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B360" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -9547,10 +9562,10 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B361" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -9561,10 +9576,10 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B362" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -9575,10 +9590,10 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B363" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C363">
         <v>1</v>
@@ -9589,10 +9604,10 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B364" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -9615,10 +9630,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>

--- a/scripts/seed-data/source/map-worlds-curation.xlsx
+++ b/scripts/seed-data/source/map-worlds-curation.xlsx
@@ -1355,6 +1355,9 @@
     <t>Arthas Moloch</t>
   </si>
   <si>
+    <t>moloch</t>
+  </si>
+  <si>
     <t>arx_tyrannus</t>
   </si>
   <si>
@@ -2715,6 +2718,12 @@
   </si>
   <si>
     <t>locationId-Override</t>
+  </si>
+  <si>
+    <t>Name-Override</t>
+  </si>
+  <si>
+    <t>WP-B1: Chart-Welt „Moloch“ = Arthas Moloch (nicht Moloch III / Molech)</t>
   </si>
 </sst>
 </file>
@@ -2852,7 +2861,7 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -6272,15 +6281,21 @@
         <v>1</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E162" t="s">
+        <v>57</v>
+      </c>
+      <c r="F162" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B163" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6292,18 +6307,18 @@
         <v>19</v>
       </c>
       <c r="F163" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K163" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B164" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -6314,10 +6329,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B165" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -6328,10 +6343,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B166" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -6342,10 +6357,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B167" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -6356,10 +6371,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B168" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -6370,10 +6385,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B169" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -6384,10 +6399,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B170" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -6398,10 +6413,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B171" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -6412,10 +6427,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B172" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -6426,24 +6441,24 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B173" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B174" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -6467,15 +6482,15 @@
         <v>29</v>
       </c>
       <c r="K174" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B175" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -6499,15 +6514,15 @@
         <v>15</v>
       </c>
       <c r="K175" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B176" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6518,10 +6533,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B177" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6530,15 +6545,15 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B178" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6549,10 +6564,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B179" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6563,10 +6578,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B180" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -6577,10 +6592,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B181" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -6591,10 +6606,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B182" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6605,10 +6620,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B183" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6620,18 +6635,18 @@
         <v>19</v>
       </c>
       <c r="F183" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K183" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B184" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -6642,10 +6657,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B185" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -6656,10 +6671,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B186" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6670,10 +6685,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B187" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -6684,10 +6699,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B188" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -6711,15 +6726,15 @@
         <v>15</v>
       </c>
       <c r="K188" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B189" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -6730,10 +6745,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B190" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -6744,10 +6759,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B191" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -6762,15 +6777,15 @@
         <v>24</v>
       </c>
       <c r="K191" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B192" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -6781,10 +6796,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B193" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6795,10 +6810,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B194" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -6809,10 +6824,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B195" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -6823,10 +6838,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B196" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -6837,10 +6852,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B197" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -6851,10 +6866,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B198" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -6865,10 +6880,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B199" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -6879,10 +6894,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B200" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -6893,10 +6908,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B201" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -6907,10 +6922,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B202" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -6921,10 +6936,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B203" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -6948,15 +6963,15 @@
         <v>15</v>
       </c>
       <c r="K203" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B204" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -6967,10 +6982,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B205" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -6994,15 +7009,15 @@
         <v>15</v>
       </c>
       <c r="K205" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B206" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -7026,15 +7041,15 @@
         <v>29</v>
       </c>
       <c r="K206" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B207" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -7045,10 +7060,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B208" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -7057,15 +7072,15 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B209" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -7080,15 +7095,15 @@
         <v>24</v>
       </c>
       <c r="K209" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B210" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -7099,10 +7114,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B211" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -7113,10 +7128,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B212" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -7131,15 +7146,15 @@
         <v>33</v>
       </c>
       <c r="K212" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B213" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -7150,10 +7165,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B214" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -7164,10 +7179,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B215" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -7178,10 +7193,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B216" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -7192,10 +7207,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B217" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -7206,10 +7221,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B218" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -7220,24 +7235,24 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B219" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B220" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -7248,10 +7263,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B221" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -7262,10 +7277,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B222" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -7276,10 +7291,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B223" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -7290,10 +7305,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B224" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -7304,10 +7319,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B225" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -7318,10 +7333,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B226" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -7345,15 +7360,15 @@
         <v>15</v>
       </c>
       <c r="K226" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B227" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -7368,15 +7383,15 @@
         <v>24</v>
       </c>
       <c r="K227" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B228" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -7387,10 +7402,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B229" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -7414,15 +7429,15 @@
         <v>15</v>
       </c>
       <c r="K229" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B230" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -7433,10 +7448,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B231" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -7456,16 +7471,16 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B232" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E232" t="s">
         <v>13</v>
@@ -7483,15 +7498,15 @@
         <v>29</v>
       </c>
       <c r="K232" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B233" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -7502,10 +7517,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B234" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -7516,10 +7531,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B235" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -7530,10 +7545,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B236" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -7544,10 +7559,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B237" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -7558,10 +7573,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B238" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -7572,10 +7587,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B239" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -7586,10 +7601,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B240" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -7600,10 +7615,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B241" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -7614,10 +7629,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B242" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7637,10 +7652,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B243" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -7651,10 +7666,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B244" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -7665,10 +7680,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B245" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -7683,15 +7698,15 @@
         <v>20</v>
       </c>
       <c r="K245" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B246" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -7706,15 +7721,15 @@
         <v>24</v>
       </c>
       <c r="K246" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B247" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -7723,15 +7738,15 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B248" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -7740,15 +7755,15 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B249" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -7763,15 +7778,15 @@
         <v>143</v>
       </c>
       <c r="K249" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B250" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -7782,10 +7797,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B251" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -7797,18 +7812,18 @@
         <v>19</v>
       </c>
       <c r="F251" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K251" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B252" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -7823,15 +7838,15 @@
         <v>33</v>
       </c>
       <c r="K252" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B253" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -7846,15 +7861,15 @@
         <v>359</v>
       </c>
       <c r="K253" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B254" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -7865,10 +7880,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B255" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -7879,10 +7894,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B256" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -7893,10 +7908,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B257" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -7907,10 +7922,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B258" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -7921,10 +7936,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B259" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -7935,10 +7950,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B260" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -7949,10 +7964,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B261" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -7963,10 +7978,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B262" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -7990,15 +8005,15 @@
         <v>15</v>
       </c>
       <c r="K262" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B263" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8009,10 +8024,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B264" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8023,10 +8038,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B265" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8037,10 +8052,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B266" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8051,10 +8066,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B267" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8065,10 +8080,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B268" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8079,10 +8094,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B269" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8097,15 +8112,15 @@
         <v>20</v>
       </c>
       <c r="K269" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B270" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8116,10 +8131,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B271" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8130,10 +8145,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B272" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8144,10 +8159,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B273" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -8162,15 +8177,15 @@
         <v>24</v>
       </c>
       <c r="K273" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B274" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -8182,18 +8197,18 @@
         <v>19</v>
       </c>
       <c r="F274" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K274" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B275" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -8204,24 +8219,24 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B276" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B277" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -8232,10 +8247,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B278" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -8246,10 +8261,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B279" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -8261,18 +8276,18 @@
         <v>19</v>
       </c>
       <c r="F279" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K279" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B280" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -8283,10 +8298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B281" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -8297,10 +8312,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B282" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -8311,10 +8326,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B283" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -8325,10 +8340,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B284" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -8339,10 +8354,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B285" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -8353,10 +8368,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B286" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -8367,10 +8382,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B287" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -8381,10 +8396,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B288" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -8395,10 +8410,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B289" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -8409,10 +8424,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B290" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -8423,10 +8438,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B291" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -8437,10 +8452,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B292" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -8464,15 +8479,15 @@
         <v>15</v>
       </c>
       <c r="K292" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B293" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -8483,10 +8498,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B294" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -8497,10 +8512,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B295" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -8511,10 +8526,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B296" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -8525,10 +8540,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B297" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -8539,10 +8554,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B298" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -8553,10 +8568,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B299" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -8580,15 +8595,15 @@
         <v>15</v>
       </c>
       <c r="K299" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B300" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -8599,10 +8614,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B301" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -8613,10 +8628,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B302" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -8627,10 +8642,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B303" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -8641,10 +8656,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B304" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -8655,10 +8670,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B305" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -8682,15 +8697,15 @@
         <v>15</v>
       </c>
       <c r="K305" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B306" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -8701,10 +8716,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B307" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -8715,10 +8730,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B308" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -8729,10 +8744,10 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B309" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -8743,10 +8758,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B310" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -8757,10 +8772,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B311" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -8771,10 +8786,10 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B312" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -8783,15 +8798,15 @@
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B313" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -8815,15 +8830,15 @@
         <v>15</v>
       </c>
       <c r="K313" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B314" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -8838,15 +8853,15 @@
         <v>24</v>
       </c>
       <c r="K314" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B315" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -8857,10 +8872,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B316" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -8871,10 +8886,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B317" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -8885,10 +8900,10 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B318" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -8899,10 +8914,10 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B319" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -8917,15 +8932,15 @@
         <v>24</v>
       </c>
       <c r="K319" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B320" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -8936,10 +8951,10 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B321" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -8950,10 +8965,10 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B322" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -8964,10 +8979,10 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B323" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -8978,10 +8993,10 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B324" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -8996,15 +9011,15 @@
         <v>87</v>
       </c>
       <c r="K324" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B325" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9015,10 +9030,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B326" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9029,10 +9044,10 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B327" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9043,10 +9058,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B328" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9055,15 +9070,15 @@
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B329" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9074,10 +9089,10 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B330" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9088,10 +9103,10 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B331" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9102,10 +9117,10 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B332" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9116,10 +9131,10 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B333" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9130,10 +9145,10 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B334" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9144,10 +9159,10 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B335" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9158,10 +9173,10 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B336" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9172,10 +9187,10 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B337" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9186,10 +9201,10 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B338" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9200,10 +9215,10 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B339" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9214,10 +9229,10 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B340" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9228,10 +9243,10 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B341" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9255,15 +9270,15 @@
         <v>29</v>
       </c>
       <c r="K341" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B342" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9275,18 +9290,18 @@
         <v>19</v>
       </c>
       <c r="F342" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K342" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B343" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9297,10 +9312,10 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B344" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9312,18 +9327,18 @@
         <v>19</v>
       </c>
       <c r="F344" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K344" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B345" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9334,10 +9349,10 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B346" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9348,10 +9363,10 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B347" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9362,10 +9377,10 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B348" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9376,10 +9391,10 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B349" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -9390,10 +9405,10 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B350" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9404,10 +9419,10 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B351" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -9418,10 +9433,10 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B352" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -9432,10 +9447,10 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B353" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -9446,10 +9461,10 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B354" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -9460,10 +9475,10 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B355" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -9474,10 +9489,10 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B356" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -9488,16 +9503,16 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B357" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E357" t="s">
         <v>13</v>
@@ -9515,15 +9530,15 @@
         <v>15</v>
       </c>
       <c r="K357" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B358" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -9534,10 +9549,10 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B359" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -9548,10 +9563,10 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B360" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -9562,10 +9577,10 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B361" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -9576,24 +9591,24 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B362" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B363" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C363">
         <v>1</v>
@@ -9604,10 +9619,10 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B364" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -9625,18 +9640,33 @@
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D2" t="s">
+        <v>902</v>
       </c>
     </row>
   </sheetData>
